--- a/Template/Thuyết minh BCTC theo Thông tư 133.xlsx
+++ b/Template/Thuyết minh BCTC theo Thông tư 133.xlsx
@@ -1,21 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DA3\Taxweb\Taxweb\Template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC79368B-1C7B-4F42-A09B-E389893C8AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15480" windowHeight="9732"/>
+    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="267">
   <si>
     <t>BẢN THUYẾT MINH BÁO CÁO TÀI CHÍNH</t>
   </si>
@@ -767,21 +784,6 @@
   <si>
     <t>(Ban hành theo Thông tư số 133/2016/TT-BTC
  ngày 26/8/2016 của Bộ Tài chính)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Hình thức sở hữu vốn: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Công ty TNHH</t>
-    </r>
   </si>
   <si>
     <r>
@@ -863,15 +865,9 @@
     <t>Địa chỉ: Số 412/32 Lê Hồng Phong - P.Thắng Tam - TP Vũng Tàu - BRVT</t>
   </si>
   <si>
-    <t>Dịch vụ</t>
-  </si>
-  <si>
     <t>01. Các khoản tiền và tương đương tiền</t>
   </si>
   <si>
-    <t>BÙI NGỌC THÂU</t>
-  </si>
-  <si>
     <t>3. Ngành nghề kinh doanh: Dịch vụ ăn uống</t>
   </si>
   <si>
@@ -879,19 +875,22 @@
   </si>
   <si>
     <t>Lập ngày 15 tháng 03 năm 2025</t>
+  </si>
+  <si>
+    <t>1. Hình thức sở hữu vốn:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="#,##0_ ;\-#,##0\ "/>
-    <numFmt numFmtId="174" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0_ ;\-#,##0\ "/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1573,9 +1572,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1901,15 +1900,15 @@
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1918,7 +1917,7 @@
     <xf numFmtId="38" fontId="3" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1930,7 +1929,7 @@
     <xf numFmtId="38" fontId="3" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1942,9 +1941,9 @@
     <xf numFmtId="38" fontId="4" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1956,12 +1955,36 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="45" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="47" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1992,26 +2015,29 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="45" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="47" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2019,33 +2045,24 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2055,20 +2072,8 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2082,29 +2087,86 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2121,6 +2183,15 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2129,101 +2200,31 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="2"/>
-    <cellStyle name="Comma 2 4" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2261,7 +2262,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2295,6 +2296,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2329,9 +2331,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2504,9 +2507,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:IE331"/>
-  <sheetFormatPr defaultColWidth="1.44140625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="1.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.44140625" style="3"/>
     <col min="2" max="3" width="3.5546875" style="3" customWidth="1"/>
@@ -2530,75 +2533,75 @@
     <col min="251" max="16384" width="1.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="46"/>
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="185" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="184" t="s">
+        <v>245</v>
+      </c>
+      <c r="I2" s="184"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="46"/>
+      <c r="B3" s="186" t="s">
         <v>261</v>
       </c>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="199"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="197" t="s">
-        <v>245</v>
-      </c>
-      <c r="I2" s="197"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="200" t="s">
-        <v>262</v>
-      </c>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="201"/>
-      <c r="F3" s="201"/>
-      <c r="G3" s="201"/>
-      <c r="H3" s="196" t="s">
+      <c r="C3" s="186"/>
+      <c r="D3" s="186"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="186"/>
+      <c r="G3" s="186"/>
+      <c r="H3" s="180" t="s">
         <v>247</v>
       </c>
-      <c r="I3" s="196"/>
-    </row>
-    <row r="4" spans="1:9" ht="25.5" customHeight="1">
+      <c r="I3" s="180"/>
+    </row>
+    <row r="4" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5"/>
       <c r="C4" s="1"/>
-      <c r="H4" s="196"/>
-      <c r="I4" s="196"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="H4" s="180"/>
+      <c r="I4" s="180"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
       <c r="C5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" ht="20.399999999999999">
+    <row r="6" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A6" s="46"/>
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="192" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="207"/>
-      <c r="D6" s="207"/>
-      <c r="E6" s="207"/>
-      <c r="F6" s="207"/>
-      <c r="G6" s="207"/>
-      <c r="H6" s="207"/>
-      <c r="I6" s="207"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="C6" s="193"/>
+      <c r="D6" s="193"/>
+      <c r="E6" s="193"/>
+      <c r="F6" s="193"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="193"/>
+      <c r="I6" s="193"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="46"/>
-      <c r="B7" s="202" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="202"/>
-      <c r="D7" s="202"/>
-      <c r="E7" s="202"/>
-      <c r="F7" s="202"/>
-      <c r="G7" s="202"/>
-      <c r="H7" s="202"/>
-      <c r="I7" s="202"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="B7" s="187" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="187"/>
+      <c r="D7" s="187"/>
+      <c r="E7" s="187"/>
+      <c r="F7" s="187"/>
+      <c r="G7" s="187"/>
+      <c r="H7" s="187"/>
+      <c r="I7" s="187"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="46"/>
       <c r="B8" s="129"/>
       <c r="C8" s="4"/>
@@ -2609,18 +2612,18 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="46"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
-      <c r="D9" s="202"/>
-      <c r="E9" s="202"/>
-      <c r="F9" s="202"/>
-      <c r="G9" s="202"/>
-      <c r="H9" s="202"/>
-      <c r="I9" s="202"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="B9" s="187"/>
+      <c r="C9" s="187"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="187"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="187"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
@@ -2629,25 +2632,22 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C11" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="C13" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C14" s="3" t="s">
         <v>3</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="107" customFormat="1">
+    <row r="15" spans="1:9" s="107" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="107" t="s">
         <v>5</v>
       </c>
@@ -2664,54 +2664,54 @@
       <c r="H15" s="108"/>
       <c r="I15" s="108"/>
     </row>
-    <row r="16" spans="1:9" s="107" customFormat="1">
+    <row r="16" spans="1:9" s="107" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C16" s="107" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F16" s="108"/>
       <c r="G16" s="108"/>
       <c r="H16" s="108" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I16" s="108"/>
     </row>
-    <row r="17" spans="2:236">
+    <row r="17" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="2:236">
+    <row r="18" spans="2:236" x14ac:dyDescent="0.3">
       <c r="C18" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="2:236" x14ac:dyDescent="0.3">
+      <c r="C19" s="8" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="19" spans="2:236">
-      <c r="C19" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" spans="2:236">
+    <row r="20" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="2:236">
+    <row r="21" spans="2:236" x14ac:dyDescent="0.3">
       <c r="C21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:236">
+    <row r="23" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:236">
+    <row r="24" spans="2:236" x14ac:dyDescent="0.3">
       <c r="C24" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:236">
+    <row r="26" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
@@ -2950,21 +2950,21 @@
       <c r="IA26" s="1"/>
       <c r="IB26" s="1"/>
     </row>
-    <row r="27" spans="2:236" ht="29.1" customHeight="1">
+    <row r="27" spans="2:236" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="205" t="s">
-        <v>256</v>
-      </c>
-      <c r="G27" s="205"/>
-      <c r="H27" s="205"/>
-      <c r="I27" s="205"/>
-    </row>
-    <row r="28" spans="2:236">
+      <c r="F27" s="198" t="s">
+        <v>255</v>
+      </c>
+      <c r="G27" s="198"/>
+      <c r="H27" s="198"/>
+      <c r="I27" s="198"/>
+    </row>
+    <row r="28" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B28" s="9" t="s">
         <v>10</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="2:236">
+    <row r="29" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>10</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="2:236">
+    <row r="30" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B30" s="9" t="s">
         <v>10</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="2:236">
+    <row r="31" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B31" s="9" t="s">
         <v>10</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="2:236">
+    <row r="32" spans="2:236" x14ac:dyDescent="0.3">
       <c r="B32" s="9" t="s">
         <v>10</v>
       </c>
@@ -3010,19 +3010,19 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D33" s="10"/>
       <c r="G33" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="9" t="s">
         <v>10</v>
       </c>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D34" s="10"/>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="9" t="s">
         <v>10</v>
       </c>
@@ -3040,34 +3040,34 @@
       </c>
       <c r="D35" s="10"/>
     </row>
-    <row r="36" spans="2:9" ht="29.1" customHeight="1">
+    <row r="36" spans="2:9" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F36" s="205" t="s">
-        <v>258</v>
-      </c>
-      <c r="G36" s="205"/>
-      <c r="H36" s="205"/>
-      <c r="I36" s="205"/>
-    </row>
-    <row r="37" spans="2:9" ht="24.9" customHeight="1">
+      <c r="F36" s="198" t="s">
+        <v>257</v>
+      </c>
+      <c r="G36" s="198"/>
+      <c r="H36" s="198"/>
+      <c r="I36" s="198"/>
+    </row>
+    <row r="37" spans="2:9" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G37" s="198" t="s">
         <v>259</v>
       </c>
-      <c r="G37" s="205" t="s">
-        <v>260</v>
-      </c>
-      <c r="H37" s="205"/>
-      <c r="I37" s="205"/>
-    </row>
-    <row r="38" spans="2:9">
+      <c r="H37" s="198"/>
+      <c r="I37" s="198"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="9" t="s">
         <v>10</v>
       </c>
@@ -3078,23 +3078,23 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="2:9">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="29" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C39" s="29"/>
       <c r="D39" s="28"/>
       <c r="E39" s="28"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="130" t="s">
+      <c r="G39" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="131"/>
+      <c r="H39" s="135"/>
       <c r="I39" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="15"/>
       <c r="C40" s="16" t="s">
         <v>26</v>
@@ -3102,15 +3102,11 @@
       <c r="D40" s="15"/>
       <c r="E40" s="15"/>
       <c r="F40" s="17"/>
-      <c r="G40" s="140">
-        <v>1264445595</v>
-      </c>
-      <c r="H40" s="141"/>
-      <c r="I40" s="109">
-        <v>1418065894</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9">
+      <c r="G40" s="148"/>
+      <c r="H40" s="149"/>
+      <c r="I40" s="109"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="20"/>
       <c r="C41" s="21" t="s">
         <v>27</v>
@@ -3118,15 +3114,11 @@
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
       <c r="F41" s="22"/>
-      <c r="G41" s="134">
-        <v>53896369</v>
-      </c>
-      <c r="H41" s="135"/>
-      <c r="I41" s="110">
-        <v>31938416</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9">
+      <c r="G41" s="142"/>
+      <c r="H41" s="143"/>
+      <c r="I41" s="110"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="24"/>
       <c r="C42" s="25" t="s">
         <v>28</v>
@@ -3134,11 +3126,11 @@
       <c r="D42" s="24"/>
       <c r="E42" s="24"/>
       <c r="F42" s="26"/>
-      <c r="G42" s="151"/>
-      <c r="H42" s="152"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="151"/>
       <c r="I42" s="124"/>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="28"/>
       <c r="C43" s="28"/>
       <c r="D43" s="29" t="s">
@@ -3146,17 +3138,17 @@
       </c>
       <c r="E43" s="28"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="153">
+      <c r="G43" s="152">
         <f>SUM(G40:H42)</f>
-        <v>1318341964</v>
-      </c>
-      <c r="H43" s="139"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="147"/>
       <c r="I43" s="125">
         <f>SUM(I40:I42)</f>
-        <v>1450004310</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="28"/>
       <c r="C44" s="28"/>
       <c r="D44" s="29"/>
@@ -3166,7 +3158,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="29" t="s">
         <v>30</v>
       </c>
@@ -3174,15 +3166,15 @@
       <c r="D45" s="28"/>
       <c r="E45" s="28"/>
       <c r="F45" s="12"/>
-      <c r="G45" s="130" t="s">
+      <c r="G45" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="131"/>
+      <c r="H45" s="135"/>
       <c r="I45" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="14.4">
+    <row r="46" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B46" s="32"/>
       <c r="C46" s="33" t="s">
         <v>31</v>
@@ -3190,11 +3182,11 @@
       <c r="D46" s="32"/>
       <c r="E46" s="15"/>
       <c r="F46" s="17"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="141"/>
+      <c r="G46" s="148"/>
+      <c r="H46" s="149"/>
       <c r="I46" s="19"/>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="34" t="s">
         <v>10</v>
       </c>
@@ -3208,7 +3200,7 @@
       <c r="H47" s="36"/>
       <c r="I47" s="37"/>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="34" t="s">
         <v>10</v>
       </c>
@@ -3222,7 +3214,7 @@
       <c r="H48" s="36"/>
       <c r="I48" s="37"/>
     </row>
-    <row r="49" spans="2:239">
+    <row r="49" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B49" s="34" t="s">
         <v>10</v>
       </c>
@@ -3236,7 +3228,7 @@
       <c r="H49" s="36"/>
       <c r="I49" s="37"/>
     </row>
-    <row r="50" spans="2:239" ht="14.4">
+    <row r="50" spans="2:239" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B50" s="20"/>
       <c r="C50" s="38" t="s">
         <v>35</v>
@@ -3244,11 +3236,11 @@
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
       <c r="F50" s="22"/>
-      <c r="G50" s="134"/>
-      <c r="H50" s="135"/>
+      <c r="G50" s="142"/>
+      <c r="H50" s="143"/>
       <c r="I50" s="41"/>
     </row>
-    <row r="51" spans="2:239">
+    <row r="51" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B51" s="42" t="s">
         <v>10</v>
       </c>
@@ -3262,7 +3254,7 @@
       <c r="H51" s="40"/>
       <c r="I51" s="41"/>
     </row>
-    <row r="52" spans="2:239">
+    <row r="52" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B52" s="42" t="s">
         <v>10</v>
       </c>
@@ -3276,7 +3268,7 @@
       <c r="H52" s="40"/>
       <c r="I52" s="41"/>
     </row>
-    <row r="53" spans="2:239" ht="14.4">
+    <row r="53" spans="2:239" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B53" s="20"/>
       <c r="C53" s="38" t="s">
         <v>39</v>
@@ -3284,11 +3276,11 @@
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
       <c r="F53" s="22"/>
-      <c r="G53" s="134"/>
-      <c r="H53" s="135"/>
+      <c r="G53" s="142"/>
+      <c r="H53" s="143"/>
       <c r="I53" s="41"/>
     </row>
-    <row r="54" spans="2:239">
+    <row r="54" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B54" s="42" t="s">
         <v>10</v>
       </c>
@@ -3298,11 +3290,11 @@
       <c r="D54" s="43"/>
       <c r="E54" s="43"/>
       <c r="F54" s="44"/>
-      <c r="G54" s="136"/>
-      <c r="H54" s="137"/>
+      <c r="G54" s="144"/>
+      <c r="H54" s="145"/>
       <c r="I54" s="41"/>
     </row>
-    <row r="55" spans="2:239">
+    <row r="55" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B55" s="45" t="s">
         <v>10</v>
       </c>
@@ -3312,11 +3304,11 @@
       <c r="D55" s="24"/>
       <c r="E55" s="24"/>
       <c r="F55" s="26"/>
-      <c r="G55" s="154"/>
-      <c r="H55" s="155"/>
+      <c r="G55" s="153"/>
+      <c r="H55" s="154"/>
       <c r="I55" s="27"/>
     </row>
-    <row r="56" spans="2:239">
+    <row r="56" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B56" s="28"/>
       <c r="C56" s="28"/>
       <c r="D56" s="29" t="s">
@@ -3324,8 +3316,8 @@
       </c>
       <c r="E56" s="28"/>
       <c r="F56" s="12"/>
-      <c r="G56" s="138"/>
-      <c r="H56" s="139"/>
+      <c r="G56" s="146"/>
+      <c r="H56" s="147"/>
       <c r="I56" s="30"/>
       <c r="J56" s="46"/>
       <c r="K56" s="46"/>
@@ -3558,7 +3550,7 @@
       <c r="ID56" s="46"/>
       <c r="IE56" s="46"/>
     </row>
-    <row r="57" spans="2:239" ht="26.25" customHeight="1">
+    <row r="57" spans="2:239" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="46"/>
       <c r="C57" s="46"/>
       <c r="D57" s="47"/>
@@ -3568,23 +3560,23 @@
       <c r="H57" s="49"/>
       <c r="I57" s="48"/>
     </row>
-    <row r="58" spans="2:239">
-      <c r="B58" s="142" t="s">
+    <row r="58" spans="2:239" x14ac:dyDescent="0.3">
+      <c r="B58" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="143"/>
-      <c r="D58" s="143"/>
-      <c r="E58" s="143"/>
-      <c r="F58" s="144"/>
-      <c r="G58" s="130" t="s">
+      <c r="C58" s="132"/>
+      <c r="D58" s="132"/>
+      <c r="E58" s="132"/>
+      <c r="F58" s="133"/>
+      <c r="G58" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H58" s="131"/>
+      <c r="H58" s="135"/>
       <c r="I58" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="2:239">
+    <row r="59" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B59" s="50" t="s">
         <v>44</v>
       </c>
@@ -3592,13 +3584,13 @@
       <c r="D59" s="15"/>
       <c r="E59" s="15"/>
       <c r="F59" s="17"/>
-      <c r="G59" s="145"/>
-      <c r="H59" s="146"/>
+      <c r="G59" s="136"/>
+      <c r="H59" s="137"/>
       <c r="I59" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:239">
+    <row r="60" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B60" s="15" t="s">
         <v>45</v>
       </c>
@@ -3606,11 +3598,11 @@
       <c r="D60" s="15"/>
       <c r="E60" s="15"/>
       <c r="F60" s="17"/>
-      <c r="G60" s="147"/>
-      <c r="H60" s="148"/>
+      <c r="G60" s="138"/>
+      <c r="H60" s="139"/>
       <c r="I60" s="37"/>
     </row>
-    <row r="61" spans="2:239">
+    <row r="61" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B61" s="20" t="s">
         <v>46</v>
       </c>
@@ -3618,11 +3610,11 @@
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="22"/>
-      <c r="G61" s="134"/>
-      <c r="H61" s="135"/>
+      <c r="G61" s="142"/>
+      <c r="H61" s="143"/>
       <c r="I61" s="41"/>
     </row>
-    <row r="62" spans="2:239">
+    <row r="62" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B62" s="20" t="s">
         <v>47</v>
       </c>
@@ -3630,11 +3622,11 @@
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
       <c r="F62" s="22"/>
-      <c r="G62" s="134"/>
-      <c r="H62" s="135"/>
+      <c r="G62" s="142"/>
+      <c r="H62" s="143"/>
       <c r="I62" s="41"/>
     </row>
-    <row r="63" spans="2:239">
+    <row r="63" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B63" s="20" t="s">
         <v>48</v>
       </c>
@@ -3642,11 +3634,11 @@
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
       <c r="F63" s="22"/>
-      <c r="G63" s="134"/>
-      <c r="H63" s="135"/>
+      <c r="G63" s="142"/>
+      <c r="H63" s="143"/>
       <c r="I63" s="41"/>
     </row>
-    <row r="64" spans="2:239">
+    <row r="64" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B64" s="20"/>
       <c r="C64" s="21" t="s">
         <v>49</v>
@@ -3654,11 +3646,11 @@
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
       <c r="F64" s="22"/>
-      <c r="G64" s="134"/>
-      <c r="H64" s="135"/>
+      <c r="G64" s="142"/>
+      <c r="H64" s="143"/>
       <c r="I64" s="41"/>
     </row>
-    <row r="65" spans="2:239">
+    <row r="65" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B65" s="20"/>
       <c r="C65" s="21" t="s">
         <v>50</v>
@@ -3666,11 +3658,11 @@
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
       <c r="F65" s="22"/>
-      <c r="G65" s="134"/>
-      <c r="H65" s="135"/>
+      <c r="G65" s="142"/>
+      <c r="H65" s="143"/>
       <c r="I65" s="41"/>
     </row>
-    <row r="66" spans="2:239">
+    <row r="66" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B66" s="20"/>
       <c r="C66" s="21" t="s">
         <v>51</v>
@@ -3678,11 +3670,11 @@
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="22"/>
-      <c r="G66" s="134"/>
-      <c r="H66" s="135"/>
+      <c r="G66" s="142"/>
+      <c r="H66" s="143"/>
       <c r="I66" s="41"/>
     </row>
-    <row r="67" spans="2:239">
+    <row r="67" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B67" s="20"/>
       <c r="C67" s="21" t="s">
         <v>52</v>
@@ -3690,11 +3682,11 @@
       <c r="D67" s="43"/>
       <c r="E67" s="43"/>
       <c r="F67" s="44"/>
-      <c r="G67" s="149"/>
-      <c r="H67" s="150"/>
+      <c r="G67" s="158"/>
+      <c r="H67" s="159"/>
       <c r="I67" s="41"/>
     </row>
-    <row r="68" spans="2:239">
+    <row r="68" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B68" s="20" t="s">
         <v>53</v>
       </c>
@@ -3702,11 +3694,11 @@
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
       <c r="F68" s="22"/>
-      <c r="G68" s="134"/>
-      <c r="H68" s="135"/>
+      <c r="G68" s="142"/>
+      <c r="H68" s="143"/>
       <c r="I68" s="41"/>
     </row>
-    <row r="69" spans="2:239">
+    <row r="69" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B69" s="51"/>
       <c r="C69" s="52" t="s">
         <v>54</v>
@@ -3714,11 +3706,11 @@
       <c r="D69" s="51"/>
       <c r="E69" s="51"/>
       <c r="F69" s="53"/>
-      <c r="G69" s="134"/>
-      <c r="H69" s="135"/>
+      <c r="G69" s="142"/>
+      <c r="H69" s="143"/>
       <c r="I69" s="54"/>
     </row>
-    <row r="70" spans="2:239">
+    <row r="70" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B70" s="51"/>
       <c r="C70" s="52" t="s">
         <v>55</v>
@@ -3726,11 +3718,11 @@
       <c r="D70" s="51"/>
       <c r="E70" s="51"/>
       <c r="F70" s="53"/>
-      <c r="G70" s="134"/>
-      <c r="H70" s="135"/>
+      <c r="G70" s="142"/>
+      <c r="H70" s="143"/>
       <c r="I70" s="54"/>
     </row>
-    <row r="71" spans="2:239">
+    <row r="71" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B71" s="51"/>
       <c r="C71" s="52" t="s">
         <v>56</v>
@@ -3738,11 +3730,11 @@
       <c r="D71" s="51"/>
       <c r="E71" s="51"/>
       <c r="F71" s="53"/>
-      <c r="G71" s="134"/>
-      <c r="H71" s="135"/>
+      <c r="G71" s="142"/>
+      <c r="H71" s="143"/>
       <c r="I71" s="54"/>
     </row>
-    <row r="72" spans="2:239">
+    <row r="72" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B72" s="51"/>
       <c r="C72" s="52" t="s">
         <v>57</v>
@@ -3750,11 +3742,11 @@
       <c r="D72" s="51"/>
       <c r="E72" s="51"/>
       <c r="F72" s="53"/>
-      <c r="G72" s="134"/>
-      <c r="H72" s="135"/>
+      <c r="G72" s="142"/>
+      <c r="H72" s="143"/>
       <c r="I72" s="54"/>
     </row>
-    <row r="73" spans="2:239">
+    <row r="73" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B73" s="51" t="s">
         <v>58</v>
       </c>
@@ -3762,11 +3754,11 @@
       <c r="D73" s="51"/>
       <c r="E73" s="51"/>
       <c r="F73" s="53"/>
-      <c r="G73" s="156"/>
-      <c r="H73" s="156"/>
+      <c r="G73" s="155"/>
+      <c r="H73" s="155"/>
       <c r="I73" s="55"/>
     </row>
-    <row r="74" spans="2:239">
+    <row r="74" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B74" s="56" t="s">
         <v>59</v>
       </c>
@@ -3774,11 +3766,11 @@
       <c r="D74" s="56"/>
       <c r="E74" s="56"/>
       <c r="F74" s="57"/>
-      <c r="G74" s="156"/>
-      <c r="H74" s="156"/>
+      <c r="G74" s="155"/>
+      <c r="H74" s="155"/>
       <c r="I74" s="58"/>
     </row>
-    <row r="75" spans="2:239">
+    <row r="75" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B75" s="59"/>
       <c r="C75" s="59"/>
       <c r="D75" s="60" t="s">
@@ -3786,11 +3778,11 @@
       </c>
       <c r="E75" s="59"/>
       <c r="F75" s="61"/>
-      <c r="G75" s="157">
+      <c r="G75" s="156">
         <f>SUM(G59:G74)</f>
         <v>0</v>
       </c>
-      <c r="H75" s="158"/>
+      <c r="H75" s="157"/>
       <c r="I75" s="62">
         <f>SUM(I59:I74)</f>
         <v>0</v>
@@ -4026,7 +4018,7 @@
       <c r="ID75" s="46"/>
       <c r="IE75" s="46"/>
     </row>
-    <row r="76" spans="2:239">
+    <row r="76" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B76" s="46"/>
       <c r="C76" s="46"/>
       <c r="D76" s="47"/>
@@ -4036,7 +4028,7 @@
       <c r="H76" s="49"/>
       <c r="I76" s="48"/>
     </row>
-    <row r="77" spans="2:239">
+    <row r="77" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B77" s="29" t="s">
         <v>60</v>
       </c>
@@ -4044,15 +4036,15 @@
       <c r="D77" s="28"/>
       <c r="E77" s="28"/>
       <c r="F77" s="12"/>
-      <c r="G77" s="130" t="s">
+      <c r="G77" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H77" s="131"/>
+      <c r="H77" s="135"/>
       <c r="I77" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="2:239">
+    <row r="78" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B78" s="34" t="s">
         <v>10</v>
       </c>
@@ -4062,11 +4054,11 @@
       <c r="D78" s="15"/>
       <c r="E78" s="15"/>
       <c r="F78" s="17"/>
-      <c r="G78" s="140"/>
-      <c r="H78" s="141"/>
+      <c r="G78" s="148"/>
+      <c r="H78" s="149"/>
       <c r="I78" s="19"/>
     </row>
-    <row r="79" spans="2:239">
+    <row r="79" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B79" s="34" t="s">
         <v>10</v>
       </c>
@@ -4076,15 +4068,11 @@
       <c r="D79" s="15"/>
       <c r="E79" s="15"/>
       <c r="F79" s="17"/>
-      <c r="G79" s="203">
-        <v>541500274</v>
-      </c>
-      <c r="H79" s="204"/>
-      <c r="I79" s="37">
-        <v>447333748</v>
-      </c>
-    </row>
-    <row r="80" spans="2:239">
+      <c r="G79" s="194"/>
+      <c r="H79" s="195"/>
+      <c r="I79" s="37"/>
+    </row>
+    <row r="80" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B80" s="42" t="s">
         <v>10</v>
       </c>
@@ -4094,15 +4082,11 @@
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
       <c r="F80" s="22"/>
-      <c r="G80" s="134">
-        <v>10376057</v>
-      </c>
-      <c r="H80" s="135"/>
-      <c r="I80" s="41">
-        <v>20469932</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9">
+      <c r="G80" s="142"/>
+      <c r="H80" s="143"/>
+      <c r="I80" s="41"/>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="42" t="s">
         <v>10</v>
       </c>
@@ -4112,11 +4096,11 @@
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
       <c r="F81" s="22"/>
-      <c r="G81" s="134"/>
-      <c r="H81" s="135"/>
+      <c r="G81" s="142"/>
+      <c r="H81" s="143"/>
       <c r="I81" s="41"/>
     </row>
-    <row r="82" spans="2:9">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="42" t="s">
         <v>10</v>
       </c>
@@ -4126,29 +4110,25 @@
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
       <c r="F82" s="22"/>
-      <c r="G82" s="134"/>
-      <c r="H82" s="135"/>
+      <c r="G82" s="142"/>
+      <c r="H82" s="143"/>
       <c r="I82" s="41"/>
     </row>
-    <row r="83" spans="2:9">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83" s="42" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
       <c r="F83" s="22"/>
-      <c r="G83" s="134">
-        <v>960405988</v>
-      </c>
-      <c r="H83" s="135"/>
-      <c r="I83" s="41">
-        <v>757881265</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9">
+      <c r="G83" s="142"/>
+      <c r="H83" s="143"/>
+      <c r="I83" s="41"/>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="45" t="s">
         <v>10</v>
       </c>
@@ -4158,11 +4138,11 @@
       <c r="D84" s="24"/>
       <c r="E84" s="24"/>
       <c r="F84" s="26"/>
-      <c r="G84" s="151"/>
-      <c r="H84" s="152"/>
+      <c r="G84" s="150"/>
+      <c r="H84" s="151"/>
       <c r="I84" s="27"/>
     </row>
-    <row r="85" spans="2:9">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="28"/>
       <c r="C85" s="28"/>
       <c r="D85" s="29" t="s">
@@ -4170,17 +4150,17 @@
       </c>
       <c r="E85" s="28"/>
       <c r="F85" s="12"/>
-      <c r="G85" s="130">
+      <c r="G85" s="134">
         <f>SUM(G78:G84)</f>
-        <v>1512282319</v>
-      </c>
-      <c r="H85" s="131"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="135"/>
       <c r="I85" s="30">
         <f>SUM(I78:I84)</f>
-        <v>1225684945</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" ht="15.75" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="46" t="s">
         <v>67</v>
       </c>
@@ -4192,55 +4172,55 @@
       <c r="H86" s="49"/>
       <c r="I86" s="63"/>
     </row>
-    <row r="87" spans="2:9" ht="15.75" customHeight="1">
-      <c r="B87" s="159" t="s">
+    <row r="87" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="C87" s="159"/>
-      <c r="D87" s="159"/>
-      <c r="E87" s="159"/>
-      <c r="F87" s="159"/>
-      <c r="G87" s="159"/>
-      <c r="H87" s="159"/>
-      <c r="I87" s="159"/>
-    </row>
-    <row r="88" spans="2:9" ht="18" customHeight="1">
-      <c r="B88" s="159" t="s">
+      <c r="C87" s="160"/>
+      <c r="D87" s="160"/>
+      <c r="E87" s="160"/>
+      <c r="F87" s="160"/>
+      <c r="G87" s="160"/>
+      <c r="H87" s="160"/>
+      <c r="I87" s="160"/>
+    </row>
+    <row r="88" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B88" s="160" t="s">
         <v>69</v>
       </c>
-      <c r="C88" s="159"/>
-      <c r="D88" s="159"/>
-      <c r="E88" s="159"/>
-      <c r="F88" s="159"/>
-      <c r="G88" s="159"/>
-      <c r="H88" s="159"/>
-      <c r="I88" s="159"/>
-    </row>
-    <row r="89" spans="2:9" ht="15" customHeight="1">
-      <c r="B89" s="159" t="s">
+      <c r="C88" s="160"/>
+      <c r="D88" s="160"/>
+      <c r="E88" s="160"/>
+      <c r="F88" s="160"/>
+      <c r="G88" s="160"/>
+      <c r="H88" s="160"/>
+      <c r="I88" s="160"/>
+    </row>
+    <row r="89" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="160" t="s">
         <v>70</v>
       </c>
-      <c r="C89" s="159"/>
-      <c r="D89" s="159"/>
-      <c r="E89" s="159"/>
-      <c r="F89" s="159"/>
-      <c r="G89" s="159"/>
-      <c r="H89" s="159"/>
-      <c r="I89" s="159"/>
-    </row>
-    <row r="90" spans="2:9">
-      <c r="B90" s="159" t="s">
+      <c r="C89" s="160"/>
+      <c r="D89" s="160"/>
+      <c r="E89" s="160"/>
+      <c r="F89" s="160"/>
+      <c r="G89" s="160"/>
+      <c r="H89" s="160"/>
+      <c r="I89" s="160"/>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90" s="160" t="s">
         <v>71</v>
       </c>
-      <c r="C90" s="159"/>
-      <c r="D90" s="159"/>
-      <c r="E90" s="159"/>
-      <c r="F90" s="159"/>
-      <c r="G90" s="159"/>
-      <c r="H90" s="159"/>
-      <c r="I90" s="159"/>
-    </row>
-    <row r="91" spans="2:9">
+      <c r="C90" s="160"/>
+      <c r="D90" s="160"/>
+      <c r="E90" s="160"/>
+      <c r="F90" s="160"/>
+      <c r="G90" s="160"/>
+      <c r="H90" s="160"/>
+      <c r="I90" s="160"/>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="46"/>
       <c r="C91" s="46"/>
       <c r="D91" s="47"/>
@@ -4250,12 +4230,12 @@
       <c r="H91" s="49"/>
       <c r="I91" s="63"/>
     </row>
-    <row r="92" spans="2:9" ht="14.4">
+    <row r="92" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B92" s="64" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="2:9">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93" s="29" t="s">
         <v>72</v>
       </c>
@@ -4267,13 +4247,13 @@
       <c r="H93" s="12"/>
       <c r="I93" s="65"/>
     </row>
-    <row r="94" spans="2:9" ht="27.6">
-      <c r="B94" s="163" t="s">
+    <row r="94" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B94" s="161" t="s">
         <v>42</v>
       </c>
-      <c r="C94" s="164"/>
-      <c r="D94" s="164"/>
-      <c r="E94" s="165"/>
+      <c r="C94" s="162"/>
+      <c r="D94" s="162"/>
+      <c r="E94" s="163"/>
       <c r="F94" s="66" t="s">
         <v>73</v>
       </c>
@@ -4287,7 +4267,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="95" spans="2:9">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95" s="67" t="s">
         <v>77</v>
       </c>
@@ -4299,7 +4279,7 @@
       <c r="H95" s="12"/>
       <c r="I95" s="65"/>
     </row>
-    <row r="96" spans="2:9">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96" s="15"/>
       <c r="C96" s="16" t="s">
         <v>78</v>
@@ -4311,7 +4291,7 @@
       <c r="H96" s="37"/>
       <c r="I96" s="37"/>
     </row>
-    <row r="97" spans="2:239">
+    <row r="97" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B97" s="20"/>
       <c r="C97" s="21" t="s">
         <v>79</v>
@@ -4323,19 +4303,25 @@
       <c r="H97" s="41"/>
       <c r="I97" s="37"/>
     </row>
-    <row r="98" spans="2:239">
+    <row r="98" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B98" s="20"/>
       <c r="C98" s="20" t="s">
         <v>80</v>
       </c>
       <c r="D98" s="43"/>
       <c r="E98" s="70"/>
-      <c r="F98" s="41"/>
+      <c r="F98" s="41">
+        <f>F96-F97</f>
+        <v>0</v>
+      </c>
       <c r="G98" s="41"/>
       <c r="H98" s="41"/>
-      <c r="I98" s="41"/>
-    </row>
-    <row r="99" spans="2:239">
+      <c r="I98" s="41">
+        <f>I96-I97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B99" s="67" t="s">
         <v>81</v>
       </c>
@@ -4347,7 +4333,7 @@
       <c r="H99" s="12"/>
       <c r="I99" s="65"/>
     </row>
-    <row r="100" spans="2:239">
+    <row r="100" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B100" s="15"/>
       <c r="C100" s="16" t="s">
         <v>78</v>
@@ -4359,7 +4345,7 @@
       <c r="H100" s="37"/>
       <c r="I100" s="37"/>
     </row>
-    <row r="101" spans="2:239">
+    <row r="101" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B101" s="20"/>
       <c r="C101" s="21" t="s">
         <v>79</v>
@@ -4371,7 +4357,7 @@
       <c r="H101" s="41"/>
       <c r="I101" s="41"/>
     </row>
-    <row r="102" spans="2:239">
+    <row r="102" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B102" s="20"/>
       <c r="C102" s="20" t="s">
         <v>80</v>
@@ -4383,7 +4369,7 @@
       <c r="H102" s="41"/>
       <c r="I102" s="41"/>
     </row>
-    <row r="103" spans="2:239">
+    <row r="103" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B103" s="67" t="s">
         <v>82</v>
       </c>
@@ -4395,7 +4381,7 @@
       <c r="H103" s="12"/>
       <c r="I103" s="65"/>
     </row>
-    <row r="104" spans="2:239">
+    <row r="104" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B104" s="15"/>
       <c r="C104" s="16" t="s">
         <v>78</v>
@@ -4407,7 +4393,7 @@
       <c r="H104" s="37"/>
       <c r="I104" s="37"/>
     </row>
-    <row r="105" spans="2:239">
+    <row r="105" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B105" s="20"/>
       <c r="C105" s="21" t="s">
         <v>79</v>
@@ -4419,7 +4405,7 @@
       <c r="H105" s="41"/>
       <c r="I105" s="41"/>
     </row>
-    <row r="106" spans="2:239">
+    <row r="106" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B106" s="24"/>
       <c r="C106" s="24" t="s">
         <v>80</v>
@@ -4661,7 +4647,7 @@
       <c r="ID106" s="10"/>
       <c r="IE106" s="10"/>
     </row>
-    <row r="107" spans="2:239">
+    <row r="107" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B107" s="72" t="s">
         <v>10</v>
       </c>
@@ -4905,7 +4891,7 @@
       <c r="ID107" s="10"/>
       <c r="IE107" s="10"/>
     </row>
-    <row r="108" spans="2:239">
+    <row r="108" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B108" s="72" t="s">
         <v>10</v>
       </c>
@@ -5149,7 +5135,7 @@
       <c r="ID108" s="10"/>
       <c r="IE108" s="10"/>
     </row>
-    <row r="109" spans="2:239">
+    <row r="109" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B109" s="72" t="s">
         <v>10</v>
       </c>
@@ -5393,7 +5379,7 @@
       <c r="ID109" s="10"/>
       <c r="IE109" s="10"/>
     </row>
-    <row r="110" spans="2:239">
+    <row r="110" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B110" s="72" t="s">
         <v>10</v>
       </c>
@@ -5637,7 +5623,7 @@
       <c r="ID110" s="10"/>
       <c r="IE110" s="10"/>
     </row>
-    <row r="111" spans="2:239">
+    <row r="111" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B111" s="72" t="s">
         <v>10</v>
       </c>
@@ -5651,7 +5637,7 @@
       <c r="H111" s="11"/>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="2:239">
+    <row r="112" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B112" s="29" t="s">
         <v>88</v>
       </c>
@@ -5663,13 +5649,13 @@
       <c r="H112" s="12"/>
       <c r="I112" s="65"/>
     </row>
-    <row r="113" spans="2:239" ht="27.6">
-      <c r="B113" s="163" t="s">
+    <row r="113" spans="2:239" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B113" s="161" t="s">
         <v>42</v>
       </c>
-      <c r="C113" s="164"/>
-      <c r="D113" s="164"/>
-      <c r="E113" s="165"/>
+      <c r="C113" s="162"/>
+      <c r="D113" s="162"/>
+      <c r="E113" s="163"/>
       <c r="F113" s="66" t="s">
         <v>73</v>
       </c>
@@ -5683,7 +5669,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="114" spans="2:239">
+    <row r="114" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B114" s="67" t="s">
         <v>89</v>
       </c>
@@ -5695,7 +5681,7 @@
       <c r="H114" s="12"/>
       <c r="I114" s="65"/>
     </row>
-    <row r="115" spans="2:239">
+    <row r="115" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B115" s="15"/>
       <c r="C115" s="16" t="s">
         <v>78</v>
@@ -5707,7 +5693,7 @@
       <c r="H115" s="37"/>
       <c r="I115" s="37"/>
     </row>
-    <row r="116" spans="2:239">
+    <row r="116" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B116" s="20"/>
       <c r="C116" s="21" t="s">
         <v>79</v>
@@ -5719,7 +5705,7 @@
       <c r="H116" s="41"/>
       <c r="I116" s="37"/>
     </row>
-    <row r="117" spans="2:239">
+    <row r="117" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B117" s="20"/>
       <c r="C117" s="20" t="s">
         <v>80</v>
@@ -5731,7 +5717,7 @@
       <c r="H117" s="41"/>
       <c r="I117" s="37"/>
     </row>
-    <row r="118" spans="2:239">
+    <row r="118" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B118" s="67" t="s">
         <v>90</v>
       </c>
@@ -5743,7 +5729,7 @@
       <c r="H118" s="12"/>
       <c r="I118" s="65"/>
     </row>
-    <row r="119" spans="2:239">
+    <row r="119" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B119" s="15"/>
       <c r="C119" s="16" t="s">
         <v>78</v>
@@ -5755,31 +5741,31 @@
       <c r="H119" s="37"/>
       <c r="I119" s="37"/>
     </row>
-    <row r="120" spans="2:239">
+    <row r="120" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B120" s="20"/>
-      <c r="C120" s="160" t="s">
+      <c r="C120" s="166" t="s">
         <v>91</v>
       </c>
-      <c r="D120" s="161"/>
-      <c r="E120" s="162"/>
+      <c r="D120" s="167"/>
+      <c r="E120" s="168"/>
       <c r="F120" s="41"/>
       <c r="G120" s="41"/>
       <c r="H120" s="41"/>
       <c r="I120" s="41"/>
     </row>
-    <row r="121" spans="2:239">
+    <row r="121" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B121" s="20"/>
-      <c r="C121" s="160" t="s">
+      <c r="C121" s="166" t="s">
         <v>92</v>
       </c>
-      <c r="D121" s="161"/>
-      <c r="E121" s="162"/>
+      <c r="D121" s="167"/>
+      <c r="E121" s="168"/>
       <c r="F121" s="41"/>
       <c r="G121" s="41"/>
       <c r="H121" s="41"/>
       <c r="I121" s="41"/>
     </row>
-    <row r="122" spans="2:239">
+    <row r="122" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B122" s="24"/>
       <c r="C122" s="24" t="s">
         <v>80</v>
@@ -6021,7 +6007,7 @@
       <c r="ID122" s="10"/>
       <c r="IE122" s="10"/>
     </row>
-    <row r="123" spans="2:239">
+    <row r="123" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B123" s="72" t="s">
         <v>10</v>
       </c>
@@ -6265,7 +6251,7 @@
       <c r="ID123" s="10"/>
       <c r="IE123" s="10"/>
     </row>
-    <row r="124" spans="2:239">
+    <row r="124" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B124" s="72" t="s">
         <v>10</v>
       </c>
@@ -6509,7 +6495,7 @@
       <c r="ID124" s="10"/>
       <c r="IE124" s="10"/>
     </row>
-    <row r="125" spans="2:239">
+    <row r="125" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B125" s="72" t="s">
         <v>10</v>
       </c>
@@ -6523,7 +6509,7 @@
       <c r="H125" s="11"/>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="2:239">
+    <row r="126" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B126" s="29" t="s">
         <v>96</v>
       </c>
@@ -6531,15 +6517,15 @@
       <c r="D126" s="28"/>
       <c r="E126" s="28"/>
       <c r="F126" s="12"/>
-      <c r="G126" s="130" t="s">
+      <c r="G126" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H126" s="131"/>
+      <c r="H126" s="135"/>
       <c r="I126" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="2:239">
+    <row r="127" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B127" s="34" t="s">
         <v>10</v>
       </c>
@@ -6549,11 +6535,11 @@
       <c r="D127" s="15"/>
       <c r="E127" s="15"/>
       <c r="F127" s="17"/>
-      <c r="G127" s="140"/>
-      <c r="H127" s="141"/>
+      <c r="G127" s="148"/>
+      <c r="H127" s="149"/>
       <c r="I127" s="19"/>
     </row>
-    <row r="128" spans="2:239">
+    <row r="128" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B128" s="34" t="s">
         <v>10</v>
       </c>
@@ -6567,7 +6553,7 @@
       <c r="H128" s="36"/>
       <c r="I128" s="37"/>
     </row>
-    <row r="129" spans="2:10">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="42" t="s">
         <v>10</v>
       </c>
@@ -6577,11 +6563,11 @@
       <c r="D129" s="20"/>
       <c r="E129" s="20"/>
       <c r="F129" s="22"/>
-      <c r="G129" s="134"/>
-      <c r="H129" s="135"/>
+      <c r="G129" s="142"/>
+      <c r="H129" s="143"/>
       <c r="I129" s="41"/>
     </row>
-    <row r="130" spans="2:10">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B130" s="28"/>
       <c r="C130" s="28"/>
       <c r="D130" s="29" t="s">
@@ -6589,15 +6575,15 @@
       </c>
       <c r="E130" s="28"/>
       <c r="F130" s="12"/>
-      <c r="G130" s="138"/>
-      <c r="H130" s="139"/>
+      <c r="G130" s="146"/>
+      <c r="H130" s="147"/>
       <c r="I130" s="76"/>
     </row>
-    <row r="131" spans="2:10" ht="14.4">
+    <row r="131" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B131" s="64"/>
       <c r="C131" s="10"/>
     </row>
-    <row r="132" spans="2:10">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B132" s="29" t="s">
         <v>106</v>
       </c>
@@ -6605,15 +6591,15 @@
       <c r="D132" s="28"/>
       <c r="E132" s="28"/>
       <c r="F132" s="12"/>
-      <c r="G132" s="130" t="s">
+      <c r="G132" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H132" s="131"/>
+      <c r="H132" s="135"/>
       <c r="I132" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="2:10">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B133" s="15"/>
       <c r="C133" s="16" t="s">
         <v>108</v>
@@ -6621,18 +6607,12 @@
       <c r="D133" s="15"/>
       <c r="E133" s="15"/>
       <c r="F133" s="17"/>
-      <c r="G133" s="140">
-        <v>30956762</v>
-      </c>
-      <c r="H133" s="141"/>
-      <c r="I133" s="19">
-        <v>40949562</v>
-      </c>
-      <c r="J133" s="213">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="134" spans="2:10">
+      <c r="G133" s="148"/>
+      <c r="H133" s="149"/>
+      <c r="I133" s="19"/>
+      <c r="J133" s="130"/>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B134" s="24"/>
       <c r="C134" s="25" t="s">
         <v>110</v>
@@ -6640,31 +6620,31 @@
       <c r="D134" s="24"/>
       <c r="E134" s="24"/>
       <c r="F134" s="26"/>
-      <c r="G134" s="154"/>
-      <c r="H134" s="155"/>
+      <c r="G134" s="153"/>
+      <c r="H134" s="154"/>
       <c r="I134" s="27"/>
     </row>
-    <row r="135" spans="2:10" ht="23.25" customHeight="1">
+    <row r="135" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="64"/>
       <c r="C135" s="10"/>
     </row>
-    <row r="136" spans="2:10">
-      <c r="B136" s="142" t="s">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B136" s="131" t="s">
         <v>111</v>
       </c>
-      <c r="C136" s="143"/>
-      <c r="D136" s="143"/>
-      <c r="E136" s="143"/>
-      <c r="F136" s="144"/>
-      <c r="G136" s="130" t="s">
+      <c r="C136" s="132"/>
+      <c r="D136" s="132"/>
+      <c r="E136" s="132"/>
+      <c r="F136" s="133"/>
+      <c r="G136" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H136" s="131"/>
+      <c r="H136" s="135"/>
       <c r="I136" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="2:10" ht="14.4">
+    <row r="137" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B137" s="32" t="s">
         <v>112</v>
       </c>
@@ -6672,11 +6652,11 @@
       <c r="D137" s="15"/>
       <c r="E137" s="15"/>
       <c r="F137" s="17"/>
-      <c r="G137" s="166"/>
-      <c r="H137" s="167"/>
+      <c r="G137" s="164"/>
+      <c r="H137" s="165"/>
       <c r="I137" s="19"/>
     </row>
-    <row r="138" spans="2:10">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B138" s="15" t="s">
         <v>113</v>
       </c>
@@ -6684,11 +6664,11 @@
       <c r="D138" s="15"/>
       <c r="E138" s="15"/>
       <c r="F138" s="17"/>
-      <c r="G138" s="168"/>
-      <c r="H138" s="169"/>
+      <c r="G138" s="170"/>
+      <c r="H138" s="171"/>
       <c r="I138" s="37"/>
     </row>
-    <row r="139" spans="2:10" ht="14.4">
+    <row r="139" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B139" s="32" t="s">
         <v>115</v>
       </c>
@@ -6696,11 +6676,11 @@
       <c r="D139" s="15"/>
       <c r="E139" s="15"/>
       <c r="F139" s="17"/>
-      <c r="G139" s="168"/>
-      <c r="H139" s="169"/>
+      <c r="G139" s="170"/>
+      <c r="H139" s="171"/>
       <c r="I139" s="37"/>
     </row>
-    <row r="140" spans="2:10">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B140" s="15" t="s">
         <v>116</v>
       </c>
@@ -6708,11 +6688,11 @@
       <c r="D140" s="15"/>
       <c r="E140" s="15"/>
       <c r="F140" s="17"/>
-      <c r="G140" s="168"/>
-      <c r="H140" s="169"/>
+      <c r="G140" s="170"/>
+      <c r="H140" s="171"/>
       <c r="I140" s="37"/>
     </row>
-    <row r="141" spans="2:10" ht="14.4">
+    <row r="141" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B141" s="32" t="s">
         <v>117</v>
       </c>
@@ -6720,11 +6700,11 @@
       <c r="D141" s="15"/>
       <c r="E141" s="15"/>
       <c r="F141" s="17"/>
-      <c r="G141" s="168"/>
-      <c r="H141" s="169"/>
+      <c r="G141" s="170"/>
+      <c r="H141" s="171"/>
       <c r="I141" s="37"/>
     </row>
-    <row r="142" spans="2:10">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B142" s="34" t="s">
         <v>10</v>
       </c>
@@ -6734,11 +6714,11 @@
       <c r="D142" s="15"/>
       <c r="E142" s="15"/>
       <c r="F142" s="17"/>
-      <c r="G142" s="168"/>
-      <c r="H142" s="169"/>
+      <c r="G142" s="170"/>
+      <c r="H142" s="171"/>
       <c r="I142" s="37"/>
     </row>
-    <row r="143" spans="2:10">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B143" s="34" t="s">
         <v>10</v>
       </c>
@@ -6748,11 +6728,11 @@
       <c r="D143" s="15"/>
       <c r="E143" s="15"/>
       <c r="F143" s="17"/>
-      <c r="G143" s="168"/>
-      <c r="H143" s="169"/>
+      <c r="G143" s="170"/>
+      <c r="H143" s="171"/>
       <c r="I143" s="37"/>
     </row>
-    <row r="144" spans="2:10">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="34" t="s">
         <v>10</v>
       </c>
@@ -6762,11 +6742,11 @@
       <c r="D144" s="15"/>
       <c r="E144" s="15"/>
       <c r="F144" s="17"/>
-      <c r="G144" s="170"/>
-      <c r="H144" s="171"/>
+      <c r="G144" s="172"/>
+      <c r="H144" s="173"/>
       <c r="I144" s="37"/>
     </row>
-    <row r="145" spans="2:239">
+    <row r="145" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B145" s="42" t="s">
         <v>121</v>
       </c>
@@ -6776,11 +6756,11 @@
       <c r="D145" s="20"/>
       <c r="E145" s="20"/>
       <c r="F145" s="22"/>
-      <c r="G145" s="134"/>
-      <c r="H145" s="135"/>
+      <c r="G145" s="142"/>
+      <c r="H145" s="143"/>
       <c r="I145" s="41"/>
     </row>
-    <row r="146" spans="2:239">
+    <row r="146" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B146" s="42" t="s">
         <v>121</v>
       </c>
@@ -6790,11 +6770,11 @@
       <c r="D146" s="20"/>
       <c r="E146" s="20"/>
       <c r="F146" s="22"/>
-      <c r="G146" s="134"/>
-      <c r="H146" s="135"/>
+      <c r="G146" s="142"/>
+      <c r="H146" s="143"/>
       <c r="I146" s="41"/>
     </row>
-    <row r="147" spans="2:239">
+    <row r="147" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B147" s="77" t="s">
         <v>121</v>
       </c>
@@ -6804,11 +6784,11 @@
       <c r="D147" s="51"/>
       <c r="E147" s="51"/>
       <c r="F147" s="53"/>
-      <c r="G147" s="134"/>
-      <c r="H147" s="135"/>
+      <c r="G147" s="142"/>
+      <c r="H147" s="143"/>
       <c r="I147" s="54"/>
     </row>
-    <row r="148" spans="2:239" ht="14.4">
+    <row r="148" spans="2:239" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B148" s="78" t="s">
         <v>125</v>
       </c>
@@ -6816,18 +6796,18 @@
       <c r="D148" s="24"/>
       <c r="E148" s="24"/>
       <c r="F148" s="26"/>
-      <c r="G148" s="154"/>
-      <c r="H148" s="155"/>
+      <c r="G148" s="153"/>
+      <c r="H148" s="154"/>
       <c r="I148" s="27"/>
     </row>
-    <row r="149" spans="2:239">
+    <row r="149" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B149" s="59"/>
       <c r="C149" s="59"/>
       <c r="D149" s="59"/>
       <c r="E149" s="59"/>
       <c r="F149" s="61"/>
-      <c r="G149" s="176"/>
-      <c r="H149" s="176"/>
+      <c r="G149" s="169"/>
+      <c r="H149" s="169"/>
       <c r="I149" s="79"/>
       <c r="J149" s="46"/>
       <c r="K149" s="46"/>
@@ -7060,7 +7040,7 @@
       <c r="ID149" s="46"/>
       <c r="IE149" s="46"/>
     </row>
-    <row r="150" spans="2:239">
+    <row r="150" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B150" s="46"/>
       <c r="C150" s="46"/>
       <c r="D150" s="47"/>
@@ -7070,7 +7050,7 @@
       <c r="H150" s="49"/>
       <c r="I150" s="48"/>
     </row>
-    <row r="151" spans="2:239">
+    <row r="151" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B151" s="29" t="s">
         <v>128</v>
       </c>
@@ -7078,15 +7058,15 @@
       <c r="D151" s="28"/>
       <c r="E151" s="28"/>
       <c r="F151" s="12"/>
-      <c r="G151" s="130" t="s">
+      <c r="G151" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H151" s="131"/>
+      <c r="H151" s="135"/>
       <c r="I151" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="2:239">
+    <row r="152" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B152" s="80"/>
       <c r="C152" s="50" t="s">
         <v>95</v>
@@ -7094,15 +7074,11 @@
       <c r="D152" s="80"/>
       <c r="E152" s="80"/>
       <c r="F152" s="81"/>
-      <c r="G152" s="172">
-        <v>70179097</v>
-      </c>
-      <c r="H152" s="173"/>
-      <c r="I152" s="19">
-        <v>85714493</v>
-      </c>
-    </row>
-    <row r="153" spans="2:239">
+      <c r="G152" s="178"/>
+      <c r="H152" s="179"/>
+      <c r="I152" s="19"/>
+    </row>
+    <row r="153" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B153" s="20"/>
       <c r="C153" s="21" t="s">
         <v>97</v>
@@ -7110,11 +7086,11 @@
       <c r="D153" s="20"/>
       <c r="E153" s="20"/>
       <c r="F153" s="22"/>
-      <c r="G153" s="174"/>
-      <c r="H153" s="175"/>
+      <c r="G153" s="176"/>
+      <c r="H153" s="177"/>
       <c r="I153" s="41"/>
     </row>
-    <row r="154" spans="2:239">
+    <row r="154" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B154" s="20"/>
       <c r="C154" s="21" t="s">
         <v>99</v>
@@ -7122,11 +7098,11 @@
       <c r="D154" s="20"/>
       <c r="E154" s="20"/>
       <c r="F154" s="22"/>
-      <c r="G154" s="174"/>
-      <c r="H154" s="175"/>
+      <c r="G154" s="176"/>
+      <c r="H154" s="177"/>
       <c r="I154" s="41"/>
     </row>
-    <row r="155" spans="2:239">
+    <row r="155" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B155" s="20"/>
       <c r="C155" s="21" t="s">
         <v>101</v>
@@ -7134,15 +7110,11 @@
       <c r="D155" s="20"/>
       <c r="E155" s="20"/>
       <c r="F155" s="22"/>
-      <c r="G155" s="149">
-        <v>23372695</v>
-      </c>
-      <c r="H155" s="150"/>
-      <c r="I155" s="41">
-        <v>6061350</v>
-      </c>
-    </row>
-    <row r="156" spans="2:239">
+      <c r="G155" s="158"/>
+      <c r="H155" s="159"/>
+      <c r="I155" s="41"/>
+    </row>
+    <row r="156" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B156" s="20"/>
       <c r="C156" s="21" t="s">
         <v>103</v>
@@ -7150,11 +7122,11 @@
       <c r="D156" s="20"/>
       <c r="E156" s="20"/>
       <c r="F156" s="22"/>
-      <c r="G156" s="149"/>
-      <c r="H156" s="150"/>
+      <c r="G156" s="158"/>
+      <c r="H156" s="159"/>
       <c r="I156" s="41"/>
     </row>
-    <row r="157" spans="2:239">
+    <row r="157" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B157" s="20"/>
       <c r="C157" s="21" t="s">
         <v>104</v>
@@ -7162,11 +7134,11 @@
       <c r="D157" s="20"/>
       <c r="E157" s="20"/>
       <c r="F157" s="22"/>
-      <c r="G157" s="174"/>
-      <c r="H157" s="175"/>
+      <c r="G157" s="176"/>
+      <c r="H157" s="177"/>
       <c r="I157" s="41"/>
     </row>
-    <row r="158" spans="2:239">
+    <row r="158" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B158" s="20"/>
       <c r="C158" s="21" t="s">
         <v>105</v>
@@ -7174,11 +7146,11 @@
       <c r="D158" s="20"/>
       <c r="E158" s="20"/>
       <c r="F158" s="22"/>
-      <c r="G158" s="174"/>
-      <c r="H158" s="175"/>
+      <c r="G158" s="176"/>
+      <c r="H158" s="177"/>
       <c r="I158" s="41"/>
     </row>
-    <row r="159" spans="2:239">
+    <row r="159" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B159" s="51"/>
       <c r="C159" s="52" t="s">
         <v>107</v>
@@ -7186,11 +7158,11 @@
       <c r="D159" s="51"/>
       <c r="E159" s="51"/>
       <c r="F159" s="53"/>
-      <c r="G159" s="174"/>
-      <c r="H159" s="175"/>
+      <c r="G159" s="176"/>
+      <c r="H159" s="177"/>
       <c r="I159" s="41"/>
     </row>
-    <row r="160" spans="2:239">
+    <row r="160" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B160" s="24"/>
       <c r="C160" s="25" t="s">
         <v>109</v>
@@ -7198,11 +7170,11 @@
       <c r="D160" s="24"/>
       <c r="E160" s="24"/>
       <c r="F160" s="26"/>
-      <c r="G160" s="132"/>
-      <c r="H160" s="133"/>
+      <c r="G160" s="140"/>
+      <c r="H160" s="141"/>
       <c r="I160" s="27"/>
     </row>
-    <row r="161" spans="2:239">
+    <row r="161" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B161" s="28"/>
       <c r="C161" s="28"/>
       <c r="D161" s="29" t="s">
@@ -7210,14 +7182,14 @@
       </c>
       <c r="E161" s="28"/>
       <c r="F161" s="12"/>
-      <c r="G161" s="177">
+      <c r="G161" s="183">
         <f>SUM(G152:H160)</f>
-        <v>93551792</v>
-      </c>
-      <c r="H161" s="131"/>
+        <v>0</v>
+      </c>
+      <c r="H161" s="135"/>
       <c r="I161" s="30">
         <f>SUM(I152:I160)</f>
-        <v>91775843</v>
+        <v>0</v>
       </c>
       <c r="J161" s="46"/>
       <c r="K161" s="46"/>
@@ -7450,7 +7422,7 @@
       <c r="ID161" s="46"/>
       <c r="IE161" s="46"/>
     </row>
-    <row r="162" spans="2:239">
+    <row r="162" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B162" s="46"/>
       <c r="C162" s="46"/>
       <c r="D162" s="47"/>
@@ -7460,7 +7432,7 @@
       <c r="H162" s="82"/>
       <c r="I162" s="48"/>
     </row>
-    <row r="163" spans="2:239">
+    <row r="163" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B163" s="29" t="s">
         <v>129</v>
       </c>
@@ -7470,15 +7442,15 @@
       <c r="F163" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G163" s="130" t="s">
+      <c r="G163" s="134" t="s">
         <v>130</v>
       </c>
-      <c r="H163" s="131"/>
+      <c r="H163" s="135"/>
       <c r="I163" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="2:239">
+    <row r="164" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B164" s="29"/>
       <c r="C164" s="29"/>
       <c r="D164" s="28"/>
@@ -7492,7 +7464,7 @@
       </c>
       <c r="I164" s="14"/>
     </row>
-    <row r="165" spans="2:239">
+    <row r="165" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B165" s="80" t="s">
         <v>133</v>
       </c>
@@ -7506,7 +7478,7 @@
       <c r="H165" s="18"/>
       <c r="I165" s="19"/>
     </row>
-    <row r="166" spans="2:239">
+    <row r="166" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B166" s="20" t="s">
         <v>135</v>
       </c>
@@ -7518,7 +7490,7 @@
       <c r="H166" s="23"/>
       <c r="I166" s="41"/>
     </row>
-    <row r="167" spans="2:239">
+    <row r="167" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B167" s="20" t="s">
         <v>136</v>
       </c>
@@ -7532,7 +7504,7 @@
       <c r="H167" s="23"/>
       <c r="I167" s="41"/>
     </row>
-    <row r="168" spans="2:239">
+    <row r="168" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B168" s="20" t="s">
         <v>135</v>
       </c>
@@ -7544,7 +7516,7 @@
       <c r="H168" s="23"/>
       <c r="I168" s="41"/>
     </row>
-    <row r="169" spans="2:239">
+    <row r="169" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B169" s="20" t="s">
         <v>138</v>
       </c>
@@ -7558,7 +7530,7 @@
       <c r="H169" s="23"/>
       <c r="I169" s="41"/>
     </row>
-    <row r="170" spans="2:239">
+    <row r="170" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B170" s="20" t="s">
         <v>140</v>
       </c>
@@ -7570,17 +7542,17 @@
       <c r="H170" s="23"/>
       <c r="I170" s="41"/>
     </row>
-    <row r="171" spans="2:239">
+    <row r="171" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B171" s="24"/>
       <c r="C171" s="24"/>
       <c r="D171" s="24"/>
       <c r="E171" s="24"/>
       <c r="F171" s="27"/>
-      <c r="G171" s="178"/>
-      <c r="H171" s="179"/>
+      <c r="G171" s="174"/>
+      <c r="H171" s="175"/>
       <c r="I171" s="27"/>
     </row>
-    <row r="172" spans="2:239">
+    <row r="172" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B172" s="28"/>
       <c r="C172" s="28"/>
       <c r="D172" s="29" t="s">
@@ -7822,7 +7794,7 @@
       <c r="ID172" s="46"/>
       <c r="IE172" s="46"/>
     </row>
-    <row r="173" spans="2:239">
+    <row r="173" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B173" s="46"/>
       <c r="C173" s="46"/>
       <c r="D173" s="47"/>
@@ -7832,23 +7804,23 @@
       <c r="H173" s="82"/>
       <c r="I173" s="48"/>
     </row>
-    <row r="174" spans="2:239">
-      <c r="B174" s="185" t="s">
+    <row r="174" spans="2:239" x14ac:dyDescent="0.3">
+      <c r="B174" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="C174" s="186"/>
-      <c r="D174" s="186"/>
-      <c r="E174" s="186"/>
-      <c r="F174" s="187"/>
-      <c r="G174" s="130" t="s">
+      <c r="C174" s="210"/>
+      <c r="D174" s="210"/>
+      <c r="E174" s="210"/>
+      <c r="F174" s="211"/>
+      <c r="G174" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="H174" s="131"/>
+      <c r="H174" s="135"/>
       <c r="I174" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="2:239">
+    <row r="175" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B175" s="83" t="s">
         <v>10</v>
       </c>
@@ -7858,11 +7830,11 @@
       <c r="D175" s="80"/>
       <c r="E175" s="80"/>
       <c r="F175" s="18"/>
-      <c r="G175" s="172"/>
-      <c r="H175" s="173"/>
+      <c r="G175" s="178"/>
+      <c r="H175" s="179"/>
       <c r="I175" s="19"/>
     </row>
-    <row r="176" spans="2:239">
+    <row r="176" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B176" s="42" t="s">
         <v>10</v>
       </c>
@@ -7872,11 +7844,11 @@
       <c r="D176" s="20"/>
       <c r="E176" s="20"/>
       <c r="F176" s="23"/>
-      <c r="G176" s="149"/>
-      <c r="H176" s="150"/>
+      <c r="G176" s="158"/>
+      <c r="H176" s="159"/>
       <c r="I176" s="41"/>
     </row>
-    <row r="177" spans="2:9">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177" s="42" t="s">
         <v>10</v>
       </c>
@@ -7886,21 +7858,21 @@
       <c r="D177" s="20"/>
       <c r="E177" s="20"/>
       <c r="F177" s="23"/>
-      <c r="G177" s="149"/>
-      <c r="H177" s="150"/>
+      <c r="G177" s="158"/>
+      <c r="H177" s="159"/>
       <c r="I177" s="41"/>
     </row>
-    <row r="178" spans="2:9">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178" s="24"/>
       <c r="C178" s="24"/>
       <c r="D178" s="24"/>
       <c r="E178" s="24"/>
       <c r="F178" s="84"/>
-      <c r="G178" s="178"/>
-      <c r="H178" s="179"/>
+      <c r="G178" s="174"/>
+      <c r="H178" s="175"/>
       <c r="I178" s="27"/>
     </row>
-    <row r="179" spans="2:9">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B179" s="28"/>
       <c r="C179" s="28"/>
       <c r="D179" s="29" t="s">
@@ -7908,11 +7880,11 @@
       </c>
       <c r="E179" s="28"/>
       <c r="F179" s="13"/>
-      <c r="G179" s="130"/>
-      <c r="H179" s="131"/>
+      <c r="G179" s="134"/>
+      <c r="H179" s="135"/>
       <c r="I179" s="30"/>
     </row>
-    <row r="180" spans="2:9">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B180" s="46"/>
       <c r="C180" s="46"/>
       <c r="D180" s="47"/>
@@ -7922,7 +7894,7 @@
       <c r="H180" s="82"/>
       <c r="I180" s="48"/>
     </row>
-    <row r="181" spans="2:9">
+    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B181" s="29" t="s">
         <v>145</v>
       </c>
@@ -7934,24 +7906,24 @@
       <c r="H181" s="29"/>
       <c r="I181" s="29"/>
     </row>
-    <row r="182" spans="2:9">
-      <c r="B182" s="180" t="s">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B182" s="201" t="s">
         <v>146</v>
       </c>
-      <c r="C182" s="181"/>
-      <c r="D182" s="181"/>
-      <c r="E182" s="184" t="s">
+      <c r="C182" s="202"/>
+      <c r="D182" s="202"/>
+      <c r="E182" s="205" t="s">
         <v>147</v>
       </c>
-      <c r="F182" s="184"/>
-      <c r="G182" s="184"/>
-      <c r="H182" s="184"/>
-      <c r="I182" s="184"/>
-    </row>
-    <row r="183" spans="2:9" ht="55.2">
-      <c r="B183" s="182"/>
-      <c r="C183" s="183"/>
-      <c r="D183" s="183"/>
+      <c r="F182" s="205"/>
+      <c r="G182" s="205"/>
+      <c r="H182" s="205"/>
+      <c r="I182" s="205"/>
+    </row>
+    <row r="183" spans="2:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="B183" s="203"/>
+      <c r="C183" s="204"/>
+      <c r="D183" s="204"/>
       <c r="E183" s="85" t="s">
         <v>148</v>
       </c>
@@ -7968,12 +7940,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="184" spans="2:9">
-      <c r="B184" s="163" t="s">
+    <row r="184" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B184" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="C184" s="164"/>
-      <c r="D184" s="164"/>
+      <c r="C184" s="162"/>
+      <c r="D184" s="162"/>
       <c r="E184" s="14">
         <v>1</v>
       </c>
@@ -7990,26 +7962,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="2:9">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B185" s="80"/>
       <c r="C185" s="80" t="s">
         <v>73</v>
       </c>
       <c r="D185" s="112"/>
-      <c r="E185" s="113">
-        <v>2500000000</v>
-      </c>
+      <c r="E185" s="113"/>
       <c r="F185" s="114"/>
       <c r="G185" s="114"/>
-      <c r="H185" s="115">
-        <v>124934224</v>
-      </c>
+      <c r="H185" s="115"/>
       <c r="I185" s="116">
         <f>E185+H185</f>
-        <v>2624934224</v>
-      </c>
-    </row>
-    <row r="186" spans="2:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B186" s="20"/>
       <c r="C186" s="20" t="s">
         <v>152</v>
@@ -8018,15 +7986,13 @@
       <c r="E186" s="126"/>
       <c r="F186" s="118"/>
       <c r="G186" s="118"/>
-      <c r="H186" s="119">
-        <v>152114180</v>
-      </c>
+      <c r="H186" s="119"/>
       <c r="I186" s="120">
         <f>E186+H186</f>
-        <v>152114180</v>
-      </c>
-    </row>
-    <row r="187" spans="2:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B187" s="20"/>
       <c r="C187" s="20" t="s">
         <v>153</v>
@@ -8035,16 +8001,13 @@
       <c r="E187" s="118"/>
       <c r="F187" s="118"/>
       <c r="G187" s="118"/>
-      <c r="H187" s="119">
-        <f>8282800+736361</f>
-        <v>9019161</v>
-      </c>
+      <c r="H187" s="119"/>
       <c r="I187" s="120">
         <f>E187+H187</f>
-        <v>9019161</v>
-      </c>
-    </row>
-    <row r="188" spans="2:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B188" s="24"/>
       <c r="C188" s="24" t="s">
         <v>76</v>
@@ -8052,20 +8015,20 @@
       <c r="D188" s="121"/>
       <c r="E188" s="111">
         <f>E185+E186-E187</f>
-        <v>2500000000</v>
+        <v>0</v>
       </c>
       <c r="F188" s="122"/>
       <c r="G188" s="122"/>
       <c r="H188" s="123">
         <f>H185-H187+H186</f>
-        <v>268029243</v>
+        <v>0</v>
       </c>
       <c r="I188" s="111">
         <f>I185+I186-I187</f>
-        <v>2768029243</v>
-      </c>
-    </row>
-    <row r="189" spans="2:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B189" s="3" t="s">
         <v>10</v>
       </c>
@@ -8079,7 +8042,7 @@
       <c r="H189" s="63"/>
       <c r="I189" s="63"/>
     </row>
-    <row r="190" spans="2:9">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B190" s="47" t="s">
         <v>155</v>
       </c>
@@ -8091,7 +8054,7 @@
       <c r="H190" s="63"/>
       <c r="I190" s="63"/>
     </row>
-    <row r="191" spans="2:9">
+    <row r="191" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B191" s="46" t="s">
         <v>156</v>
       </c>
@@ -8103,7 +8066,7 @@
       <c r="H191" s="63"/>
       <c r="I191" s="63"/>
     </row>
-    <row r="192" spans="2:9">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B192" s="46" t="s">
         <v>157</v>
       </c>
@@ -8115,7 +8078,7 @@
       <c r="H192" s="63"/>
       <c r="I192" s="63"/>
     </row>
-    <row r="193" spans="2:9">
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B193" s="46" t="s">
         <v>158</v>
       </c>
@@ -8127,7 +8090,7 @@
       <c r="H193" s="63"/>
       <c r="I193" s="63"/>
     </row>
-    <row r="194" spans="2:9">
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B194" s="46" t="s">
         <v>161</v>
       </c>
@@ -8139,7 +8102,7 @@
       <c r="H194" s="63"/>
       <c r="I194" s="63"/>
     </row>
-    <row r="195" spans="2:9">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B195" s="46" t="s">
         <v>10</v>
       </c>
@@ -8153,7 +8116,7 @@
       <c r="H195" s="63"/>
       <c r="I195" s="63"/>
     </row>
-    <row r="196" spans="2:9">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B196" s="46" t="s">
         <v>10</v>
       </c>
@@ -8167,7 +8130,7 @@
       <c r="H196" s="63"/>
       <c r="I196" s="63"/>
     </row>
-    <row r="197" spans="2:9">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B197" s="46" t="s">
         <v>166</v>
       </c>
@@ -8179,7 +8142,7 @@
       <c r="H197" s="63"/>
       <c r="I197" s="63"/>
     </row>
-    <row r="198" spans="2:9">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B198" s="46" t="s">
         <v>167</v>
       </c>
@@ -8191,7 +8154,7 @@
       <c r="H198" s="63"/>
       <c r="I198" s="63"/>
     </row>
-    <row r="199" spans="2:9">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B199" s="46" t="s">
         <v>168</v>
       </c>
@@ -8203,7 +8166,7 @@
       <c r="H199" s="63"/>
       <c r="I199" s="63"/>
     </row>
-    <row r="200" spans="2:9">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B200" s="46" t="s">
         <v>169</v>
       </c>
@@ -8215,7 +8178,7 @@
       <c r="H200" s="63"/>
       <c r="I200" s="63"/>
     </row>
-    <row r="201" spans="2:9">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B201" s="46" t="s">
         <v>170</v>
       </c>
@@ -8227,9 +8190,9 @@
       <c r="H201" s="63"/>
       <c r="I201" s="63"/>
     </row>
-    <row r="202" spans="2:9">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B202" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C202" s="46"/>
       <c r="D202" s="46"/>
@@ -8239,7 +8202,7 @@
       <c r="H202" s="63"/>
       <c r="I202" s="63"/>
     </row>
-    <row r="203" spans="2:9">
+    <row r="203" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B203" s="46" t="s">
         <v>171</v>
       </c>
@@ -8251,7 +8214,7 @@
       <c r="H203" s="63"/>
       <c r="I203" s="63"/>
     </row>
-    <row r="204" spans="2:9">
+    <row r="204" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B204" s="47" t="s">
         <v>172</v>
       </c>
@@ -8263,7 +8226,7 @@
       <c r="H204" s="63"/>
       <c r="I204" s="63"/>
     </row>
-    <row r="205" spans="2:9">
+    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B205" s="46"/>
       <c r="C205" s="46"/>
       <c r="D205" s="46"/>
@@ -8273,7 +8236,7 @@
       <c r="H205" s="63"/>
       <c r="I205" s="63"/>
     </row>
-    <row r="206" spans="2:9">
+    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B206" s="29" t="s">
         <v>173</v>
       </c>
@@ -8285,7 +8248,7 @@
       <c r="H206" s="12"/>
       <c r="I206" s="65"/>
     </row>
-    <row r="207" spans="2:9">
+    <row r="207" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B207" s="29" t="s">
         <v>174</v>
       </c>
@@ -8293,15 +8256,15 @@
       <c r="D207" s="28"/>
       <c r="E207" s="28"/>
       <c r="F207" s="65"/>
-      <c r="G207" s="177" t="s">
+      <c r="G207" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H207" s="131"/>
+      <c r="H207" s="135"/>
       <c r="I207" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="208" spans="2:9">
+    <row r="208" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B208" s="50" t="s">
         <v>175</v>
       </c>
@@ -8309,17 +8272,17 @@
       <c r="D208" s="80"/>
       <c r="E208" s="80"/>
       <c r="F208" s="18"/>
-      <c r="G208" s="192">
+      <c r="G208" s="199">
         <f>G209+G210+G211</f>
-        <v>3659457710</v>
-      </c>
-      <c r="H208" s="193"/>
+        <v>0</v>
+      </c>
+      <c r="H208" s="200"/>
       <c r="I208" s="19">
         <f>SUM(I209:I212)</f>
-        <v>4139316829</v>
-      </c>
-    </row>
-    <row r="209" spans="2:239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B209" s="88" t="s">
         <v>10</v>
       </c>
@@ -8329,15 +8292,11 @@
       <c r="D209" s="15"/>
       <c r="E209" s="15"/>
       <c r="F209" s="89"/>
-      <c r="G209" s="188">
-        <v>480617732</v>
-      </c>
-      <c r="H209" s="189"/>
-      <c r="I209" s="37">
-        <v>849521325</v>
-      </c>
-    </row>
-    <row r="210" spans="2:239">
+      <c r="G209" s="181"/>
+      <c r="H209" s="182"/>
+      <c r="I209" s="37"/>
+    </row>
+    <row r="210" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B210" s="88" t="s">
         <v>10</v>
       </c>
@@ -8347,15 +8306,11 @@
       <c r="D210" s="15"/>
       <c r="E210" s="15"/>
       <c r="F210" s="89"/>
-      <c r="G210" s="188">
-        <v>3178839978</v>
-      </c>
-      <c r="H210" s="189"/>
-      <c r="I210" s="37">
-        <v>3289795504</v>
-      </c>
-    </row>
-    <row r="211" spans="2:239">
+      <c r="G210" s="181"/>
+      <c r="H210" s="182"/>
+      <c r="I210" s="37"/>
+    </row>
+    <row r="211" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B211" s="88" t="s">
         <v>10</v>
       </c>
@@ -8365,11 +8320,11 @@
       <c r="D211" s="15"/>
       <c r="E211" s="15"/>
       <c r="F211" s="89"/>
-      <c r="G211" s="188"/>
-      <c r="H211" s="189"/>
+      <c r="G211" s="181"/>
+      <c r="H211" s="182"/>
       <c r="I211" s="37"/>
     </row>
-    <row r="212" spans="2:239">
+    <row r="212" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B212" s="88" t="s">
         <v>10</v>
       </c>
@@ -8379,8 +8334,8 @@
       <c r="D212" s="15"/>
       <c r="E212" s="15"/>
       <c r="F212" s="89"/>
-      <c r="G212" s="188"/>
-      <c r="H212" s="189"/>
+      <c r="G212" s="181"/>
+      <c r="H212" s="182"/>
       <c r="I212" s="37"/>
       <c r="J212" s="1"/>
       <c r="K212" s="1"/>
@@ -8613,7 +8568,7 @@
       <c r="ID212" s="1"/>
       <c r="IE212" s="1"/>
     </row>
-    <row r="213" spans="2:239">
+    <row r="213" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B213" s="90"/>
       <c r="C213" s="90"/>
       <c r="D213" s="90" t="s">
@@ -8621,17 +8576,17 @@
       </c>
       <c r="E213" s="90"/>
       <c r="F213" s="91"/>
-      <c r="G213" s="190">
+      <c r="G213" s="188">
         <f>SUM(G209:G212)</f>
-        <v>3659457710</v>
-      </c>
-      <c r="H213" s="191"/>
+        <v>0</v>
+      </c>
+      <c r="H213" s="189"/>
       <c r="I213" s="94">
         <f>SUM(I209:I212)</f>
-        <v>4139316829</v>
-      </c>
-    </row>
-    <row r="214" spans="2:239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B214" s="16" t="s">
         <v>180</v>
       </c>
@@ -8639,11 +8594,11 @@
       <c r="D214" s="15"/>
       <c r="E214" s="15"/>
       <c r="F214" s="89"/>
-      <c r="G214" s="190"/>
-      <c r="H214" s="191"/>
+      <c r="G214" s="188"/>
+      <c r="H214" s="189"/>
       <c r="I214" s="37"/>
     </row>
-    <row r="215" spans="2:239">
+    <row r="215" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B215" s="16" t="s">
         <v>181</v>
       </c>
@@ -8651,11 +8606,11 @@
       <c r="D215" s="15"/>
       <c r="E215" s="15"/>
       <c r="F215" s="89"/>
-      <c r="G215" s="190"/>
-      <c r="H215" s="191"/>
+      <c r="G215" s="188"/>
+      <c r="H215" s="189"/>
       <c r="I215" s="37"/>
     </row>
-    <row r="216" spans="2:239">
+    <row r="216" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B216" s="16" t="s">
         <v>182</v>
       </c>
@@ -8663,11 +8618,11 @@
       <c r="D216" s="15"/>
       <c r="E216" s="15"/>
       <c r="F216" s="89"/>
-      <c r="G216" s="190"/>
-      <c r="H216" s="191"/>
+      <c r="G216" s="188"/>
+      <c r="H216" s="189"/>
       <c r="I216" s="37"/>
     </row>
-    <row r="217" spans="2:239">
+    <row r="217" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B217" s="16" t="s">
         <v>183</v>
       </c>
@@ -8675,11 +8630,11 @@
       <c r="D217" s="15"/>
       <c r="E217" s="15"/>
       <c r="F217" s="89"/>
-      <c r="G217" s="190"/>
-      <c r="H217" s="191"/>
+      <c r="G217" s="188"/>
+      <c r="H217" s="189"/>
       <c r="I217" s="37"/>
     </row>
-    <row r="218" spans="2:239">
+    <row r="218" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B218" s="16" t="s">
         <v>184</v>
       </c>
@@ -8687,11 +8642,11 @@
       <c r="D218" s="15"/>
       <c r="E218" s="15"/>
       <c r="F218" s="89"/>
-      <c r="G218" s="190"/>
-      <c r="H218" s="191"/>
+      <c r="G218" s="188"/>
+      <c r="H218" s="189"/>
       <c r="I218" s="37"/>
     </row>
-    <row r="219" spans="2:239">
+    <row r="219" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B219" s="16" t="s">
         <v>185</v>
       </c>
@@ -8699,11 +8654,11 @@
       <c r="D219" s="15"/>
       <c r="E219" s="15"/>
       <c r="F219" s="89"/>
-      <c r="G219" s="190"/>
-      <c r="H219" s="191"/>
+      <c r="G219" s="188"/>
+      <c r="H219" s="189"/>
       <c r="I219" s="37"/>
     </row>
-    <row r="220" spans="2:239">
+    <row r="220" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B220" s="95" t="s">
         <v>186</v>
       </c>
@@ -8711,8 +8666,8 @@
       <c r="D220" s="46"/>
       <c r="E220" s="46"/>
       <c r="F220" s="96"/>
-      <c r="G220" s="178"/>
-      <c r="H220" s="179"/>
+      <c r="G220" s="174"/>
+      <c r="H220" s="175"/>
       <c r="I220" s="37"/>
       <c r="J220" s="1"/>
       <c r="K220" s="1"/>
@@ -8945,7 +8900,7 @@
       <c r="ID220" s="1"/>
       <c r="IE220" s="1"/>
     </row>
-    <row r="221" spans="2:239">
+    <row r="221" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B221" s="29" t="s">
         <v>187</v>
       </c>
@@ -8953,15 +8908,15 @@
       <c r="D221" s="29"/>
       <c r="E221" s="29"/>
       <c r="F221" s="13"/>
-      <c r="G221" s="177" t="s">
+      <c r="G221" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H221" s="131"/>
+      <c r="H221" s="135"/>
       <c r="I221" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="222" spans="2:239">
+    <row r="222" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B222" s="97" t="s">
         <v>10</v>
       </c>
@@ -8971,11 +8926,11 @@
       <c r="D222" s="15"/>
       <c r="E222" s="15"/>
       <c r="F222" s="89"/>
-      <c r="G222" s="188"/>
-      <c r="H222" s="189"/>
+      <c r="G222" s="181"/>
+      <c r="H222" s="182"/>
       <c r="I222" s="41"/>
     </row>
-    <row r="223" spans="2:239">
+    <row r="223" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B223" s="88" t="s">
         <v>10</v>
       </c>
@@ -8985,11 +8940,11 @@
       <c r="D223" s="20"/>
       <c r="E223" s="20"/>
       <c r="F223" s="23"/>
-      <c r="G223" s="149"/>
-      <c r="H223" s="150"/>
+      <c r="G223" s="158"/>
+      <c r="H223" s="159"/>
       <c r="I223" s="41"/>
     </row>
-    <row r="224" spans="2:239">
+    <row r="224" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B224" s="88" t="s">
         <v>10</v>
       </c>
@@ -8999,8 +8954,8 @@
       <c r="D224" s="20"/>
       <c r="E224" s="20"/>
       <c r="F224" s="23"/>
-      <c r="G224" s="188"/>
-      <c r="H224" s="189"/>
+      <c r="G224" s="181"/>
+      <c r="H224" s="182"/>
       <c r="I224" s="41"/>
       <c r="J224" s="1"/>
       <c r="K224" s="1"/>
@@ -9233,7 +9188,7 @@
       <c r="ID224" s="1"/>
       <c r="IE224" s="1"/>
     </row>
-    <row r="225" spans="2:239">
+    <row r="225" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B225" s="98"/>
       <c r="C225" s="98"/>
       <c r="D225" s="98" t="s">
@@ -9241,8 +9196,8 @@
       </c>
       <c r="E225" s="98"/>
       <c r="F225" s="99"/>
-      <c r="G225" s="194"/>
-      <c r="H225" s="195"/>
+      <c r="G225" s="190"/>
+      <c r="H225" s="191"/>
       <c r="I225" s="94"/>
       <c r="J225" s="1"/>
       <c r="K225" s="1"/>
@@ -9475,7 +9430,7 @@
       <c r="ID225" s="1"/>
       <c r="IE225" s="1"/>
     </row>
-    <row r="226" spans="2:239">
+    <row r="226" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B226" s="29" t="s">
         <v>191</v>
       </c>
@@ -9483,15 +9438,15 @@
       <c r="D226" s="29"/>
       <c r="E226" s="29"/>
       <c r="F226" s="13"/>
-      <c r="G226" s="177" t="s">
+      <c r="G226" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H226" s="131"/>
+      <c r="H226" s="135"/>
       <c r="I226" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="227" spans="2:239">
+    <row r="227" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B227" s="97" t="s">
         <v>10</v>
       </c>
@@ -9501,15 +9456,11 @@
       <c r="D227" s="15"/>
       <c r="E227" s="15"/>
       <c r="F227" s="89"/>
-      <c r="G227" s="188">
-        <v>2094939930</v>
-      </c>
-      <c r="H227" s="189"/>
-      <c r="I227" s="41">
-        <v>2879955446</v>
-      </c>
-    </row>
-    <row r="228" spans="2:239">
+      <c r="G227" s="181"/>
+      <c r="H227" s="182"/>
+      <c r="I227" s="41"/>
+    </row>
+    <row r="228" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B228" s="88" t="s">
         <v>10</v>
       </c>
@@ -9519,11 +9470,11 @@
       <c r="D228" s="20"/>
       <c r="E228" s="20"/>
       <c r="F228" s="23"/>
-      <c r="G228" s="203"/>
-      <c r="H228" s="204"/>
+      <c r="G228" s="194"/>
+      <c r="H228" s="195"/>
       <c r="I228" s="41"/>
     </row>
-    <row r="229" spans="2:239">
+    <row r="229" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B229" s="88" t="s">
         <v>10</v>
       </c>
@@ -9533,11 +9484,11 @@
       <c r="D229" s="20"/>
       <c r="E229" s="20"/>
       <c r="F229" s="23"/>
-      <c r="G229" s="188"/>
-      <c r="H229" s="189"/>
+      <c r="G229" s="181"/>
+      <c r="H229" s="182"/>
       <c r="I229" s="41"/>
     </row>
-    <row r="230" spans="2:239">
+    <row r="230" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B230" s="88" t="s">
         <v>10</v>
       </c>
@@ -9547,11 +9498,11 @@
       <c r="D230" s="20"/>
       <c r="E230" s="20"/>
       <c r="F230" s="23"/>
-      <c r="G230" s="188"/>
-      <c r="H230" s="189"/>
+      <c r="G230" s="181"/>
+      <c r="H230" s="182"/>
       <c r="I230" s="41"/>
     </row>
-    <row r="231" spans="2:239">
+    <row r="231" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B231" s="88" t="s">
         <v>10</v>
       </c>
@@ -9561,11 +9512,11 @@
       <c r="D231" s="20"/>
       <c r="E231" s="20"/>
       <c r="F231" s="23"/>
-      <c r="G231" s="188"/>
-      <c r="H231" s="189"/>
+      <c r="G231" s="181"/>
+      <c r="H231" s="182"/>
       <c r="I231" s="41"/>
     </row>
-    <row r="232" spans="2:239">
+    <row r="232" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B232" s="88" t="s">
         <v>10</v>
       </c>
@@ -9575,8 +9526,8 @@
       <c r="D232" s="20"/>
       <c r="E232" s="20"/>
       <c r="F232" s="23"/>
-      <c r="G232" s="188"/>
-      <c r="H232" s="189"/>
+      <c r="G232" s="181"/>
+      <c r="H232" s="182"/>
       <c r="I232" s="41"/>
       <c r="J232" s="1"/>
       <c r="K232" s="1"/>
@@ -9809,7 +9760,7 @@
       <c r="ID232" s="1"/>
       <c r="IE232" s="1"/>
     </row>
-    <row r="233" spans="2:239">
+    <row r="233" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B233" s="98"/>
       <c r="C233" s="98"/>
       <c r="D233" s="98" t="s">
@@ -9817,14 +9768,14 @@
       </c>
       <c r="E233" s="98"/>
       <c r="F233" s="99"/>
-      <c r="G233" s="190">
+      <c r="G233" s="188">
         <f>SUM(G227:G232)</f>
-        <v>2094939930</v>
-      </c>
-      <c r="H233" s="191"/>
+        <v>0</v>
+      </c>
+      <c r="H233" s="189"/>
       <c r="I233" s="94">
         <f>SUM(I227:I232)</f>
-        <v>2879955446</v>
+        <v>0</v>
       </c>
       <c r="J233" s="1"/>
       <c r="K233" s="1"/>
@@ -10057,7 +10008,7 @@
       <c r="ID233" s="1"/>
       <c r="IE233" s="1"/>
     </row>
-    <row r="234" spans="2:239">
+    <row r="234" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B234" s="29" t="s">
         <v>198</v>
       </c>
@@ -10065,15 +10016,15 @@
       <c r="D234" s="29"/>
       <c r="E234" s="29"/>
       <c r="F234" s="13"/>
-      <c r="G234" s="177" t="s">
+      <c r="G234" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H234" s="131"/>
+      <c r="H234" s="135"/>
       <c r="I234" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="235" spans="2:239">
+    <row r="235" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B235" s="97" t="s">
         <v>10</v>
       </c>
@@ -10083,15 +10034,11 @@
       <c r="D235" s="15"/>
       <c r="E235" s="15"/>
       <c r="F235" s="89"/>
-      <c r="G235" s="172">
-        <v>44682</v>
-      </c>
-      <c r="H235" s="173"/>
-      <c r="I235" s="41">
-        <v>30157</v>
-      </c>
-    </row>
-    <row r="236" spans="2:239">
+      <c r="G235" s="178"/>
+      <c r="H235" s="179"/>
+      <c r="I235" s="41"/>
+    </row>
+    <row r="236" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B236" s="88" t="s">
         <v>10</v>
       </c>
@@ -10101,11 +10048,11 @@
       <c r="D236" s="20"/>
       <c r="E236" s="20"/>
       <c r="F236" s="23"/>
-      <c r="G236" s="149"/>
-      <c r="H236" s="150"/>
+      <c r="G236" s="158"/>
+      <c r="H236" s="159"/>
       <c r="I236" s="41"/>
     </row>
-    <row r="237" spans="2:239">
+    <row r="237" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B237" s="88" t="s">
         <v>10</v>
       </c>
@@ -10115,11 +10062,11 @@
       <c r="D237" s="20"/>
       <c r="E237" s="20"/>
       <c r="F237" s="23"/>
-      <c r="G237" s="149"/>
-      <c r="H237" s="150"/>
+      <c r="G237" s="158"/>
+      <c r="H237" s="159"/>
       <c r="I237" s="41"/>
     </row>
-    <row r="238" spans="2:239">
+    <row r="238" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B238" s="88" t="s">
         <v>10</v>
       </c>
@@ -10129,11 +10076,11 @@
       <c r="D238" s="20"/>
       <c r="E238" s="20"/>
       <c r="F238" s="23"/>
-      <c r="G238" s="149"/>
-      <c r="H238" s="150"/>
+      <c r="G238" s="158"/>
+      <c r="H238" s="159"/>
       <c r="I238" s="41"/>
     </row>
-    <row r="239" spans="2:239">
+    <row r="239" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B239" s="88" t="s">
         <v>10</v>
       </c>
@@ -10143,11 +10090,11 @@
       <c r="D239" s="20"/>
       <c r="E239" s="20"/>
       <c r="F239" s="23"/>
-      <c r="G239" s="149"/>
-      <c r="H239" s="150"/>
+      <c r="G239" s="158"/>
+      <c r="H239" s="159"/>
       <c r="I239" s="41"/>
     </row>
-    <row r="240" spans="2:239">
+    <row r="240" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B240" s="88" t="s">
         <v>10</v>
       </c>
@@ -10157,8 +10104,8 @@
       <c r="D240" s="20"/>
       <c r="E240" s="20"/>
       <c r="F240" s="23"/>
-      <c r="G240" s="149"/>
-      <c r="H240" s="150"/>
+      <c r="G240" s="158"/>
+      <c r="H240" s="159"/>
       <c r="I240" s="41"/>
       <c r="J240" s="1"/>
       <c r="K240" s="1"/>
@@ -10389,7 +10336,7 @@
       <c r="IB240" s="1"/>
       <c r="IC240" s="1"/>
     </row>
-    <row r="241" spans="2:239">
+    <row r="241" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B241" s="98"/>
       <c r="C241" s="98"/>
       <c r="D241" s="98" t="s">
@@ -10397,11 +10344,11 @@
       </c>
       <c r="E241" s="98"/>
       <c r="F241" s="99"/>
-      <c r="G241" s="132">
+      <c r="G241" s="140">
         <f>G235</f>
-        <v>44682</v>
-      </c>
-      <c r="H241" s="133"/>
+        <v>0</v>
+      </c>
+      <c r="H241" s="141"/>
       <c r="I241" s="94">
         <f>I240</f>
         <v>0</v>
@@ -10637,7 +10584,7 @@
       <c r="ID241" s="1"/>
       <c r="IE241" s="1"/>
     </row>
-    <row r="242" spans="2:239">
+    <row r="242" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B242" s="29" t="s">
         <v>205</v>
       </c>
@@ -10645,15 +10592,15 @@
       <c r="D242" s="29"/>
       <c r="E242" s="29"/>
       <c r="F242" s="13"/>
-      <c r="G242" s="177" t="s">
+      <c r="G242" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H242" s="131"/>
+      <c r="H242" s="135"/>
       <c r="I242" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="243" spans="2:239">
+    <row r="243" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B243" s="97" t="s">
         <v>10</v>
       </c>
@@ -10663,11 +10610,11 @@
       <c r="D243" s="15"/>
       <c r="E243" s="15"/>
       <c r="F243" s="89"/>
-      <c r="G243" s="172"/>
-      <c r="H243" s="173"/>
+      <c r="G243" s="178"/>
+      <c r="H243" s="179"/>
       <c r="I243" s="41"/>
     </row>
-    <row r="244" spans="2:239">
+    <row r="244" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B244" s="88" t="s">
         <v>10</v>
       </c>
@@ -10677,11 +10624,11 @@
       <c r="D244" s="20"/>
       <c r="E244" s="20"/>
       <c r="F244" s="23"/>
-      <c r="G244" s="149"/>
-      <c r="H244" s="150"/>
+      <c r="G244" s="158"/>
+      <c r="H244" s="159"/>
       <c r="I244" s="41"/>
     </row>
-    <row r="245" spans="2:239">
+    <row r="245" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B245" s="88" t="s">
         <v>10</v>
       </c>
@@ -10691,11 +10638,11 @@
       <c r="D245" s="20"/>
       <c r="E245" s="20"/>
       <c r="F245" s="23"/>
-      <c r="G245" s="149"/>
-      <c r="H245" s="150"/>
+      <c r="G245" s="158"/>
+      <c r="H245" s="159"/>
       <c r="I245" s="41"/>
     </row>
-    <row r="246" spans="2:239">
+    <row r="246" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B246" s="88" t="s">
         <v>10</v>
       </c>
@@ -10705,11 +10652,11 @@
       <c r="D246" s="20"/>
       <c r="E246" s="20"/>
       <c r="F246" s="23"/>
-      <c r="G246" s="149"/>
-      <c r="H246" s="150"/>
+      <c r="G246" s="158"/>
+      <c r="H246" s="159"/>
       <c r="I246" s="41"/>
     </row>
-    <row r="247" spans="2:239">
+    <row r="247" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B247" s="88" t="s">
         <v>10</v>
       </c>
@@ -10719,11 +10666,11 @@
       <c r="D247" s="20"/>
       <c r="E247" s="20"/>
       <c r="F247" s="23"/>
-      <c r="G247" s="149"/>
-      <c r="H247" s="150"/>
+      <c r="G247" s="158"/>
+      <c r="H247" s="159"/>
       <c r="I247" s="41"/>
     </row>
-    <row r="248" spans="2:239">
+    <row r="248" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B248" s="88" t="s">
         <v>10</v>
       </c>
@@ -10733,11 +10680,11 @@
       <c r="D248" s="20"/>
       <c r="E248" s="20"/>
       <c r="F248" s="23"/>
-      <c r="G248" s="149"/>
-      <c r="H248" s="150"/>
+      <c r="G248" s="158"/>
+      <c r="H248" s="159"/>
       <c r="I248" s="41"/>
     </row>
-    <row r="249" spans="2:239">
+    <row r="249" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B249" s="88" t="s">
         <v>10</v>
       </c>
@@ -10747,11 +10694,11 @@
       <c r="D249" s="20"/>
       <c r="E249" s="20"/>
       <c r="F249" s="23"/>
-      <c r="G249" s="149"/>
-      <c r="H249" s="150"/>
+      <c r="G249" s="158"/>
+      <c r="H249" s="159"/>
       <c r="I249" s="41"/>
     </row>
-    <row r="250" spans="2:239">
+    <row r="250" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B250" s="100" t="s">
         <v>10</v>
       </c>
@@ -10761,8 +10708,8 @@
       <c r="D250" s="51"/>
       <c r="E250" s="51"/>
       <c r="F250" s="101"/>
-      <c r="G250" s="178"/>
-      <c r="H250" s="179"/>
+      <c r="G250" s="174"/>
+      <c r="H250" s="175"/>
       <c r="I250" s="41"/>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
@@ -10995,7 +10942,7 @@
       <c r="ID250" s="1"/>
       <c r="IE250" s="1"/>
     </row>
-    <row r="251" spans="2:239">
+    <row r="251" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B251" s="29" t="s">
         <v>214</v>
       </c>
@@ -11003,15 +10950,15 @@
       <c r="D251" s="29"/>
       <c r="E251" s="29"/>
       <c r="F251" s="13"/>
-      <c r="G251" s="177" t="s">
+      <c r="G251" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H251" s="131"/>
+      <c r="H251" s="135"/>
       <c r="I251" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="252" spans="2:239">
+    <row r="252" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B252" s="15"/>
       <c r="C252" s="15" t="s">
         <v>215</v>
@@ -11019,15 +10966,11 @@
       <c r="D252" s="15"/>
       <c r="E252" s="15"/>
       <c r="F252" s="89"/>
-      <c r="G252" s="172">
-        <v>185058124</v>
-      </c>
-      <c r="H252" s="173"/>
-      <c r="I252" s="41">
-        <v>200250637</v>
-      </c>
-    </row>
-    <row r="253" spans="2:239">
+      <c r="G252" s="178"/>
+      <c r="H252" s="179"/>
+      <c r="I252" s="41"/>
+    </row>
+    <row r="253" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B253" s="20"/>
       <c r="C253" s="20" t="s">
         <v>216</v>
@@ -11035,15 +10978,11 @@
       <c r="D253" s="20"/>
       <c r="E253" s="20"/>
       <c r="F253" s="23"/>
-      <c r="G253" s="149">
-        <v>1195609943</v>
-      </c>
-      <c r="H253" s="150"/>
-      <c r="I253" s="41">
-        <v>989151313</v>
-      </c>
-    </row>
-    <row r="254" spans="2:239">
+      <c r="G253" s="158"/>
+      <c r="H253" s="159"/>
+      <c r="I253" s="41"/>
+    </row>
+    <row r="254" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B254" s="20"/>
       <c r="C254" s="20" t="s">
         <v>217</v>
@@ -11051,11 +10990,11 @@
       <c r="D254" s="20"/>
       <c r="E254" s="20"/>
       <c r="F254" s="23"/>
-      <c r="G254" s="149"/>
-      <c r="H254" s="150"/>
+      <c r="G254" s="158"/>
+      <c r="H254" s="159"/>
       <c r="I254" s="41"/>
     </row>
-    <row r="255" spans="2:239">
+    <row r="255" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B255" s="20"/>
       <c r="C255" s="21" t="s">
         <v>218</v>
@@ -11063,11 +11002,11 @@
       <c r="D255" s="20"/>
       <c r="E255" s="20"/>
       <c r="F255" s="23"/>
-      <c r="G255" s="149"/>
-      <c r="H255" s="150"/>
+      <c r="G255" s="158"/>
+      <c r="H255" s="159"/>
       <c r="I255" s="41"/>
     </row>
-    <row r="256" spans="2:239">
+    <row r="256" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B256" s="51"/>
       <c r="C256" s="52" t="s">
         <v>219</v>
@@ -11075,8 +11014,8 @@
       <c r="D256" s="51"/>
       <c r="E256" s="51"/>
       <c r="F256" s="101"/>
-      <c r="G256" s="149"/>
-      <c r="H256" s="150"/>
+      <c r="G256" s="158"/>
+      <c r="H256" s="159"/>
       <c r="I256" s="41"/>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -11309,7 +11248,7 @@
       <c r="ID256" s="1"/>
       <c r="IE256" s="1"/>
     </row>
-    <row r="257" spans="2:239">
+    <row r="257" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B257" s="98"/>
       <c r="C257" s="98"/>
       <c r="D257" s="98" t="s">
@@ -11317,14 +11256,14 @@
       </c>
       <c r="E257" s="98"/>
       <c r="F257" s="99"/>
-      <c r="G257" s="132">
+      <c r="G257" s="140">
         <f>SUM(G252:H253)</f>
-        <v>1380668067</v>
-      </c>
-      <c r="H257" s="133"/>
+        <v>0</v>
+      </c>
+      <c r="H257" s="141"/>
       <c r="I257" s="94">
         <f>SUM(I252:I256)</f>
-        <v>1189401950</v>
+        <v>0</v>
       </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -11557,7 +11496,7 @@
       <c r="ID257" s="1"/>
       <c r="IE257" s="1"/>
     </row>
-    <row r="258" spans="2:239">
+    <row r="258" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B258" s="29" t="s">
         <v>220</v>
       </c>
@@ -11565,10 +11504,10 @@
       <c r="D258" s="29"/>
       <c r="E258" s="29"/>
       <c r="F258" s="13"/>
-      <c r="G258" s="177" t="s">
+      <c r="G258" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H258" s="131"/>
+      <c r="H258" s="135"/>
       <c r="I258" s="14" t="s">
         <v>127</v>
       </c>
@@ -11803,7 +11742,7 @@
       <c r="ID258" s="1"/>
       <c r="IE258" s="1"/>
     </row>
-    <row r="259" spans="2:239">
+    <row r="259" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B259" s="97" t="s">
         <v>10</v>
       </c>
@@ -11813,8 +11752,8 @@
       <c r="D259" s="102"/>
       <c r="E259" s="102"/>
       <c r="F259" s="103"/>
-      <c r="G259" s="210"/>
-      <c r="H259" s="211"/>
+      <c r="G259" s="196"/>
+      <c r="H259" s="197"/>
       <c r="I259" s="94"/>
       <c r="J259" s="1"/>
       <c r="K259" s="1"/>
@@ -12047,7 +11986,7 @@
       <c r="ID259" s="1"/>
       <c r="IE259" s="1"/>
     </row>
-    <row r="260" spans="2:239">
+    <row r="260" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B260" s="88" t="s">
         <v>10</v>
       </c>
@@ -12291,7 +12230,7 @@
       <c r="ID260" s="1"/>
       <c r="IE260" s="1"/>
     </row>
-    <row r="261" spans="2:239">
+    <row r="261" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B261" s="88" t="s">
         <v>10</v>
       </c>
@@ -12535,7 +12474,7 @@
       <c r="ID261" s="1"/>
       <c r="IE261" s="1"/>
     </row>
-    <row r="262" spans="2:239">
+    <row r="262" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B262" s="88" t="s">
         <v>10</v>
       </c>
@@ -12549,7 +12488,7 @@
       <c r="H262" s="93"/>
       <c r="I262" s="94"/>
     </row>
-    <row r="263" spans="2:239">
+    <row r="263" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B263" s="42" t="s">
         <v>10</v>
       </c>
@@ -12559,13 +12498,9 @@
       <c r="D263" s="20"/>
       <c r="E263" s="20"/>
       <c r="F263" s="23"/>
-      <c r="G263" s="149">
-        <v>6248330</v>
-      </c>
-      <c r="H263" s="150"/>
-      <c r="I263" s="41">
-        <v>10317166</v>
-      </c>
+      <c r="G263" s="158"/>
+      <c r="H263" s="159"/>
+      <c r="I263" s="41"/>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
       <c r="L263" s="1"/>
@@ -12797,7 +12732,7 @@
       <c r="ID263" s="1"/>
       <c r="IE263" s="1"/>
     </row>
-    <row r="264" spans="2:239">
+    <row r="264" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B264" s="98"/>
       <c r="C264" s="98"/>
       <c r="D264" s="98" t="s">
@@ -12805,14 +12740,14 @@
       </c>
       <c r="E264" s="98"/>
       <c r="F264" s="99"/>
-      <c r="G264" s="132">
+      <c r="G264" s="140">
         <f>SUM(G263)</f>
-        <v>6248330</v>
-      </c>
-      <c r="H264" s="133"/>
+        <v>0</v>
+      </c>
+      <c r="H264" s="141"/>
       <c r="I264" s="94">
         <f>SUM(I263)</f>
-        <v>10317166</v>
+        <v>0</v>
       </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -13045,7 +12980,7 @@
       <c r="ID264" s="1"/>
       <c r="IE264" s="1"/>
     </row>
-    <row r="265" spans="2:239">
+    <row r="265" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B265" s="29" t="s">
         <v>225</v>
       </c>
@@ -13053,10 +12988,10 @@
       <c r="D265" s="29"/>
       <c r="E265" s="29"/>
       <c r="F265" s="13"/>
-      <c r="G265" s="177" t="s">
+      <c r="G265" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H265" s="131"/>
+      <c r="H265" s="135"/>
       <c r="I265" s="14" t="s">
         <v>127</v>
       </c>
@@ -13291,7 +13226,7 @@
       <c r="ID265" s="1"/>
       <c r="IE265" s="1"/>
     </row>
-    <row r="266" spans="2:239">
+    <row r="266" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B266" s="97" t="s">
         <v>10</v>
       </c>
@@ -13301,8 +13236,8 @@
       <c r="D266" s="102"/>
       <c r="E266" s="102"/>
       <c r="F266" s="103"/>
-      <c r="G266" s="210"/>
-      <c r="H266" s="211"/>
+      <c r="G266" s="196"/>
+      <c r="H266" s="197"/>
       <c r="I266" s="94"/>
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
@@ -13535,7 +13470,7 @@
       <c r="ID266" s="1"/>
       <c r="IE266" s="1"/>
     </row>
-    <row r="267" spans="2:239">
+    <row r="267" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B267" s="88" t="s">
         <v>10</v>
       </c>
@@ -13545,8 +13480,8 @@
       <c r="D267" s="90"/>
       <c r="E267" s="90"/>
       <c r="F267" s="91"/>
-      <c r="G267" s="174"/>
-      <c r="H267" s="175"/>
+      <c r="G267" s="176"/>
+      <c r="H267" s="177"/>
       <c r="I267" s="94"/>
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
@@ -13779,7 +13714,7 @@
       <c r="ID267" s="1"/>
       <c r="IE267" s="1"/>
     </row>
-    <row r="268" spans="2:239">
+    <row r="268" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B268" s="88" t="s">
         <v>10</v>
       </c>
@@ -13789,11 +13724,11 @@
       <c r="D268" s="90"/>
       <c r="E268" s="90"/>
       <c r="F268" s="91"/>
-      <c r="G268" s="149"/>
-      <c r="H268" s="150"/>
+      <c r="G268" s="158"/>
+      <c r="H268" s="159"/>
       <c r="I268" s="41"/>
     </row>
-    <row r="269" spans="2:239">
+    <row r="269" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B269" s="42" t="s">
         <v>10</v>
       </c>
@@ -13803,15 +13738,13 @@
       <c r="D269" s="20"/>
       <c r="E269" s="20"/>
       <c r="F269" s="23"/>
-      <c r="G269" s="149">
-        <v>9019151</v>
-      </c>
-      <c r="H269" s="150"/>
+      <c r="G269" s="158"/>
+      <c r="H269" s="159"/>
       <c r="I269" s="41">
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="2:239">
+    <row r="270" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B270" s="98"/>
       <c r="C270" s="98"/>
       <c r="D270" s="98" t="s">
@@ -13819,17 +13752,17 @@
       </c>
       <c r="E270" s="98"/>
       <c r="F270" s="99"/>
-      <c r="G270" s="132">
+      <c r="G270" s="140">
         <f>SUM(G268:G269)</f>
-        <v>9019151</v>
-      </c>
-      <c r="H270" s="133"/>
+        <v>0</v>
+      </c>
+      <c r="H270" s="141"/>
       <c r="I270" s="94">
         <f>SUM(I268:I269)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="2:239">
+    <row r="271" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B271" s="29" t="s">
         <v>229</v>
       </c>
@@ -13837,15 +13770,15 @@
       <c r="D271" s="28"/>
       <c r="E271" s="28"/>
       <c r="F271" s="65"/>
-      <c r="G271" s="177" t="s">
+      <c r="G271" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="H271" s="131"/>
+      <c r="H271" s="135"/>
       <c r="I271" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="272" spans="2:239">
+    <row r="272" spans="2:239" x14ac:dyDescent="0.3">
       <c r="B272" s="104" t="s">
         <v>10</v>
       </c>
@@ -13855,15 +13788,11 @@
       <c r="D272" s="46"/>
       <c r="E272" s="46"/>
       <c r="F272" s="96"/>
-      <c r="G272" s="172">
-        <v>38028545</v>
-      </c>
-      <c r="H272" s="173"/>
-      <c r="I272" s="114">
-        <v>16061350</v>
-      </c>
-    </row>
-    <row r="273" spans="2:9">
+      <c r="G272" s="178"/>
+      <c r="H272" s="179"/>
+      <c r="I272" s="114"/>
+    </row>
+    <row r="273" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B273" s="100"/>
       <c r="C273" s="52" t="s">
         <v>231</v>
@@ -13871,11 +13800,11 @@
       <c r="D273" s="51"/>
       <c r="E273" s="51"/>
       <c r="F273" s="101"/>
-      <c r="G273" s="149"/>
-      <c r="H273" s="150"/>
+      <c r="G273" s="158"/>
+      <c r="H273" s="159"/>
       <c r="I273" s="127"/>
     </row>
-    <row r="274" spans="2:9">
+    <row r="274" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B274" s="100" t="s">
         <v>10</v>
       </c>
@@ -13885,11 +13814,11 @@
       <c r="D274" s="51"/>
       <c r="E274" s="51"/>
       <c r="F274" s="101"/>
-      <c r="G274" s="149"/>
-      <c r="H274" s="150"/>
+      <c r="G274" s="158"/>
+      <c r="H274" s="159"/>
       <c r="I274" s="127"/>
     </row>
-    <row r="275" spans="2:9">
+    <row r="275" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B275" s="98"/>
       <c r="C275" s="52" t="s">
         <v>233</v>
@@ -13897,11 +13826,11 @@
       <c r="D275" s="51"/>
       <c r="E275" s="51"/>
       <c r="F275" s="101"/>
-      <c r="G275" s="149"/>
-      <c r="H275" s="150"/>
+      <c r="G275" s="158"/>
+      <c r="H275" s="159"/>
       <c r="I275" s="127"/>
     </row>
-    <row r="276" spans="2:9">
+    <row r="276" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B276" s="45" t="s">
         <v>10</v>
       </c>
@@ -13911,32 +13840,38 @@
       <c r="D276" s="24"/>
       <c r="E276" s="24"/>
       <c r="F276" s="84"/>
-      <c r="G276" s="178"/>
-      <c r="H276" s="179"/>
-      <c r="I276" s="128"/>
-    </row>
-    <row r="277" spans="2:9">
+      <c r="G276" s="174">
+        <f>G272</f>
+        <v>0</v>
+      </c>
+      <c r="H276" s="175"/>
+      <c r="I276" s="128">
+        <f>I272</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B277" s="1" t="s">
         <v>235</v>
       </c>
       <c r="C277" s="1"/>
     </row>
-    <row r="278" spans="2:9">
+    <row r="278" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B278" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="279" spans="2:9" hidden="1">
+    <row r="279" spans="2:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="B279" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="280" spans="2:9">
+    <row r="280" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B280" s="3" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="282" spans="2:9">
+    <row r="282" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B282" s="47" t="s">
         <v>239</v>
       </c>
@@ -13948,7 +13883,7 @@
       <c r="H282" s="48"/>
       <c r="I282" s="48"/>
     </row>
-    <row r="283" spans="2:9">
+    <row r="283" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B283" s="105">
         <v>1</v>
       </c>
@@ -13962,7 +13897,7 @@
       <c r="H283" s="48"/>
       <c r="I283" s="48"/>
     </row>
-    <row r="284" spans="2:9">
+    <row r="284" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B284" s="105">
         <v>2</v>
       </c>
@@ -13976,7 +13911,7 @@
       <c r="H284" s="48"/>
       <c r="I284" s="48"/>
     </row>
-    <row r="285" spans="2:9">
+    <row r="285" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B285" s="105">
         <v>3</v>
       </c>
@@ -13990,7 +13925,7 @@
       <c r="H285" s="48"/>
       <c r="I285" s="48"/>
     </row>
-    <row r="286" spans="2:9" hidden="1">
+    <row r="286" spans="2:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="B286" s="105">
         <v>4</v>
       </c>
@@ -14004,7 +13939,7 @@
       <c r="H286" s="48"/>
       <c r="I286" s="48"/>
     </row>
-    <row r="287" spans="2:9">
+    <row r="287" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B287" s="105">
         <v>5</v>
       </c>
@@ -14018,158 +13953,156 @@
       <c r="H287" s="48"/>
       <c r="I287" s="48"/>
     </row>
-    <row r="289" spans="2:9">
+    <row r="289" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B289" s="1"/>
     </row>
-    <row r="290" spans="2:9" ht="14.4" customHeight="1">
+    <row r="290" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F290" s="11"/>
       <c r="G290" s="11"/>
-      <c r="H290" s="208" t="s">
-        <v>268</v>
-      </c>
-      <c r="I290" s="208"/>
-    </row>
-    <row r="291" spans="2:9" ht="14.4" customHeight="1">
+      <c r="H290" s="207" t="s">
+        <v>265</v>
+      </c>
+      <c r="I290" s="207"/>
+    </row>
+    <row r="291" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C291" s="6"/>
       <c r="D291" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F291" s="209" t="s">
+      <c r="F291" s="206" t="s">
         <v>246</v>
       </c>
-      <c r="G291" s="209"/>
-      <c r="H291" s="209" t="s">
+      <c r="G291" s="206"/>
+      <c r="H291" s="206" t="s">
         <v>160</v>
       </c>
-      <c r="I291" s="209"/>
-    </row>
-    <row r="292" spans="2:9" ht="14.4" customHeight="1">
+      <c r="I291" s="206"/>
+    </row>
+    <row r="292" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C292" s="106"/>
       <c r="D292" s="106" t="s">
         <v>162</v>
       </c>
-      <c r="F292" s="212" t="s">
+      <c r="F292" s="208" t="s">
         <v>162</v>
       </c>
-      <c r="G292" s="212"/>
-      <c r="H292" s="208" t="s">
+      <c r="G292" s="208"/>
+      <c r="H292" s="207" t="s">
         <v>163</v>
       </c>
-      <c r="I292" s="208"/>
-    </row>
-    <row r="295" spans="2:9">
+      <c r="I292" s="207"/>
+    </row>
+    <row r="295" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B295" s="7"/>
     </row>
-    <row r="296" spans="2:9">
+    <row r="296" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B296" s="7"/>
     </row>
-    <row r="297" spans="2:9">
+    <row r="297" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B297" s="7"/>
-      <c r="H297" s="209" t="s">
-        <v>265</v>
-      </c>
-      <c r="I297" s="209"/>
-    </row>
-    <row r="298" spans="2:9">
+      <c r="H297" s="206"/>
+      <c r="I297" s="206"/>
+    </row>
+    <row r="298" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B298" s="7"/>
     </row>
-    <row r="299" spans="2:9">
+    <row r="299" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B299" s="7"/>
     </row>
-    <row r="300" spans="2:9">
+    <row r="300" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B300" s="7"/>
     </row>
-    <row r="301" spans="2:9">
+    <row r="301" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B301" s="7"/>
     </row>
-    <row r="302" spans="2:9">
+    <row r="302" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B302" s="7"/>
     </row>
-    <row r="303" spans="2:9">
+    <row r="303" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B303" s="7"/>
     </row>
-    <row r="304" spans="2:9">
+    <row r="304" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B304" s="7"/>
     </row>
-    <row r="305" spans="2:2">
+    <row r="305" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B305" s="7"/>
     </row>
-    <row r="306" spans="2:2">
+    <row r="306" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B306" s="7"/>
     </row>
-    <row r="307" spans="2:2">
+    <row r="307" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B307" s="7"/>
     </row>
-    <row r="308" spans="2:2">
+    <row r="308" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B308" s="7"/>
     </row>
-    <row r="309" spans="2:2">
+    <row r="309" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B309" s="7"/>
     </row>
-    <row r="310" spans="2:2">
+    <row r="310" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B310" s="7"/>
     </row>
-    <row r="311" spans="2:2">
+    <row r="311" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B311" s="7"/>
     </row>
-    <row r="312" spans="2:2">
+    <row r="312" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B312" s="7"/>
     </row>
-    <row r="313" spans="2:2">
+    <row r="313" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B313" s="7"/>
     </row>
-    <row r="314" spans="2:2">
+    <row r="314" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B314" s="7"/>
     </row>
-    <row r="315" spans="2:2">
+    <row r="315" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B315" s="7"/>
     </row>
-    <row r="316" spans="2:2">
+    <row r="316" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B316" s="7"/>
     </row>
-    <row r="317" spans="2:2">
+    <row r="317" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B317" s="7"/>
     </row>
-    <row r="318" spans="2:2">
+    <row r="318" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B318" s="7"/>
     </row>
-    <row r="319" spans="2:2">
+    <row r="319" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B319" s="7"/>
     </row>
-    <row r="320" spans="2:2">
+    <row r="320" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B320" s="7"/>
     </row>
-    <row r="321" spans="2:2">
+    <row r="321" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B321" s="7"/>
     </row>
-    <row r="322" spans="2:2">
+    <row r="322" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B322" s="7"/>
     </row>
-    <row r="323" spans="2:2">
+    <row r="323" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B323" s="7"/>
     </row>
-    <row r="324" spans="2:2">
+    <row r="324" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B324" s="7"/>
     </row>
-    <row r="325" spans="2:2">
+    <row r="325" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B325" s="7"/>
     </row>
-    <row r="326" spans="2:2">
+    <row r="326" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B326" s="7"/>
     </row>
-    <row r="327" spans="2:2">
+    <row r="327" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B327" s="7"/>
     </row>
-    <row r="328" spans="2:2">
+    <row r="328" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B328" s="7"/>
     </row>
-    <row r="329" spans="2:2">
+    <row r="329" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B329" s="7"/>
     </row>
-    <row r="330" spans="2:2">
+    <row r="330" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B330" s="7"/>
     </row>
-    <row r="331" spans="2:2">
+    <row r="331" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B331" s="7"/>
     </row>
   </sheetData>
@@ -14186,6 +14119,18 @@
     <mergeCell ref="G265:H265"/>
     <mergeCell ref="H290:I290"/>
     <mergeCell ref="H291:I291"/>
+    <mergeCell ref="G276:H276"/>
+    <mergeCell ref="G269:H269"/>
+    <mergeCell ref="G270:H270"/>
+    <mergeCell ref="G271:H271"/>
+    <mergeCell ref="G272:H272"/>
+    <mergeCell ref="G274:H274"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="G174:H174"/>
+    <mergeCell ref="G175:H175"/>
+    <mergeCell ref="G176:H176"/>
+    <mergeCell ref="G160:H160"/>
+    <mergeCell ref="G161:H161"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="G245:H245"/>
     <mergeCell ref="G246:H246"/>
@@ -14197,6 +14142,19 @@
     <mergeCell ref="F27:I27"/>
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G264:H264"/>
+    <mergeCell ref="G263:H263"/>
+    <mergeCell ref="G212:H212"/>
+    <mergeCell ref="G213:H213"/>
+    <mergeCell ref="B184:D184"/>
+    <mergeCell ref="G207:H207"/>
+    <mergeCell ref="G208:H208"/>
+    <mergeCell ref="G209:H209"/>
+    <mergeCell ref="G177:H177"/>
+    <mergeCell ref="G178:H178"/>
+    <mergeCell ref="G179:H179"/>
+    <mergeCell ref="B182:D183"/>
+    <mergeCell ref="E182:I182"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="G248:H248"/>
     <mergeCell ref="G239:H239"/>
@@ -14207,13 +14165,20 @@
     <mergeCell ref="G258:H258"/>
     <mergeCell ref="G228:H228"/>
     <mergeCell ref="G229:H229"/>
-    <mergeCell ref="G264:H264"/>
     <mergeCell ref="G255:H255"/>
     <mergeCell ref="G256:H256"/>
     <mergeCell ref="G238:H238"/>
     <mergeCell ref="G230:H230"/>
     <mergeCell ref="G250:H250"/>
     <mergeCell ref="G235:H235"/>
+    <mergeCell ref="G247:H247"/>
+    <mergeCell ref="G254:H254"/>
+    <mergeCell ref="G249:H249"/>
+    <mergeCell ref="G251:H251"/>
+    <mergeCell ref="G216:H216"/>
+    <mergeCell ref="G217:H217"/>
+    <mergeCell ref="G210:H210"/>
+    <mergeCell ref="G211:H211"/>
     <mergeCell ref="H3:I4"/>
     <mergeCell ref="G232:H232"/>
     <mergeCell ref="G244:H244"/>
@@ -14224,17 +14189,6 @@
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="G242:H242"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="G276:H276"/>
-    <mergeCell ref="G269:H269"/>
-    <mergeCell ref="G270:H270"/>
-    <mergeCell ref="G271:H271"/>
-    <mergeCell ref="G272:H272"/>
-    <mergeCell ref="G247:H247"/>
-    <mergeCell ref="G254:H254"/>
-    <mergeCell ref="G249:H249"/>
-    <mergeCell ref="G263:H263"/>
-    <mergeCell ref="G274:H274"/>
-    <mergeCell ref="G251:H251"/>
     <mergeCell ref="G233:H233"/>
     <mergeCell ref="G234:H234"/>
     <mergeCell ref="G243:H243"/>
@@ -14249,27 +14203,6 @@
     <mergeCell ref="G221:H221"/>
     <mergeCell ref="G214:H214"/>
     <mergeCell ref="G215:H215"/>
-    <mergeCell ref="G216:H216"/>
-    <mergeCell ref="G217:H217"/>
-    <mergeCell ref="G210:H210"/>
-    <mergeCell ref="G211:H211"/>
-    <mergeCell ref="G212:H212"/>
-    <mergeCell ref="G213:H213"/>
-    <mergeCell ref="B184:D184"/>
-    <mergeCell ref="G207:H207"/>
-    <mergeCell ref="G208:H208"/>
-    <mergeCell ref="G209:H209"/>
-    <mergeCell ref="G177:H177"/>
-    <mergeCell ref="G178:H178"/>
-    <mergeCell ref="G179:H179"/>
-    <mergeCell ref="B182:D183"/>
-    <mergeCell ref="E182:I182"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="G174:H174"/>
-    <mergeCell ref="G175:H175"/>
-    <mergeCell ref="G176:H176"/>
-    <mergeCell ref="G160:H160"/>
-    <mergeCell ref="G161:H161"/>
     <mergeCell ref="G163:H163"/>
     <mergeCell ref="G171:H171"/>
     <mergeCell ref="G155:H155"/>
@@ -14316,7 +14249,6 @@
     <mergeCell ref="G81:H81"/>
     <mergeCell ref="G82:H82"/>
     <mergeCell ref="G83:H83"/>
-    <mergeCell ref="G74:H74"/>
     <mergeCell ref="G75:H75"/>
     <mergeCell ref="G77:H77"/>
     <mergeCell ref="G78:H78"/>
@@ -14327,15 +14259,6 @@
     <mergeCell ref="G67:H67"/>
     <mergeCell ref="G68:H68"/>
     <mergeCell ref="G69:H69"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G50:H50"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="G58:H58"/>
     <mergeCell ref="G59:H59"/>
@@ -14350,6 +14273,16 @@
     <mergeCell ref="G61:H61"/>
     <mergeCell ref="G62:H62"/>
     <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="G74:H74"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.16" right="0.16" top="0.23" bottom="0.16" header="0.23" footer="0.16"/>
@@ -14358,9 +14291,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Template/Thuyết minh BCTC theo Thông tư 133.xlsx
+++ b/Template/Thuyết minh BCTC theo Thông tư 133.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DA3\Taxweb\Taxweb\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC79368B-1C7B-4F42-A09B-E389893C8AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A300AE99-35E2-4CEF-8FD4-65013E3B7FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7559,10 +7559,16 @@
         <v>29</v>
       </c>
       <c r="E172" s="28"/>
-      <c r="F172" s="30"/>
+      <c r="F172" s="30">
+        <f>SUM(F165:F171)</f>
+        <v>0</v>
+      </c>
       <c r="G172" s="30"/>
       <c r="H172" s="30"/>
-      <c r="I172" s="30"/>
+      <c r="I172" s="30">
+        <f>SUM(I165:I171)</f>
+        <v>0</v>
+      </c>
       <c r="J172" s="46"/>
       <c r="K172" s="46"/>
       <c r="L172" s="46"/>
